--- a/UPDATE 24 JULI.xlsx
+++ b/UPDATE 24 JULI.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMN\Documents\Projek\Projectg\AWAKENING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F722244A-B59A-4F7A-889B-E10061DFF265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB52034A-7659-4AF1-9494-493901CD1AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="240" windowWidth="29040" windowHeight="16080" activeTab="5" xr2:uid="{B793076F-8D73-466D-B30A-FF91CE4E6F62}"/>
+    <workbookView xWindow="-120" yWindow="240" windowWidth="29040" windowHeight="16080" xr2:uid="{B793076F-8D73-466D-B30A-FF91CE4E6F62}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="192">
   <si>
     <t>TS_NAME</t>
   </si>
@@ -944,7 +944,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1048,6 +1048,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1405,6 +1406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992F0BB8-1CA9-4379-9049-AB6F95C27E32}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1551,11 +1553,11 @@
       </c>
       <c r="K3" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D3,BIO!A:A,0),2)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3" s="15">
         <f t="shared" ref="L3:L66" si="0">IF(K3-J3&lt;=0,0,K3-J3)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D3,'BIO WAHYU'!B:B,0),4)</f>
@@ -1894,11 +1896,11 @@
       </c>
       <c r="K10" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D10,BIO!A:A,0),2)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10" s="15">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D10,'BIO WAHYU'!B:B,0),4)</f>
@@ -2090,11 +2092,11 @@
       </c>
       <c r="K14" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D14,BIO!A:A,0),2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D14,'BIO WAHYU'!B:B,0),4)</f>
@@ -2286,11 +2288,11 @@
       </c>
       <c r="K18" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D18,BIO!A:A,0),2)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L18" s="15">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M18" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D18,'BIO WAHYU'!B:B,0),4)</f>
@@ -2335,11 +2337,11 @@
       </c>
       <c r="K19" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D19,BIO!A:A,0),2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="15">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D19,'BIO WAHYU'!B:B,0),4)</f>
@@ -3462,11 +3464,11 @@
       </c>
       <c r="K42" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D42,BIO!A:A,0),2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="15">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D42,'BIO WAHYU'!B:B,0),4)</f>
@@ -3756,11 +3758,11 @@
       </c>
       <c r="K48" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D48,BIO!A:A,0),2)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L48" s="15">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M48" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D48,'BIO WAHYU'!B:B,0),4)</f>
@@ -4050,11 +4052,11 @@
       </c>
       <c r="K54" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D54,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D54,'BIO WAHYU'!B:B,0),4)</f>
@@ -4099,11 +4101,11 @@
       </c>
       <c r="K55" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D55,BIO!A:A,0),2)</f>
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L55" s="15">
         <f t="shared" si="0"/>
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M55" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D55,'BIO WAHYU'!B:B,0),4)</f>
@@ -4246,11 +4248,11 @@
       </c>
       <c r="K58" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D58,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D58,'BIO WAHYU'!B:B,0),4)</f>
@@ -4295,11 +4297,11 @@
       </c>
       <c r="K59" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D59,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L59" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M59" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D59,'BIO WAHYU'!B:B,0),4)</f>
@@ -4442,11 +4444,11 @@
       </c>
       <c r="K62" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D62,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D62,'BIO WAHYU'!B:B,0),4)</f>
@@ -4491,11 +4493,11 @@
       </c>
       <c r="K63" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D63,BIO!A:A,0),2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="15">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D63,'BIO WAHYU'!B:B,0),4)</f>
@@ -4638,11 +4640,11 @@
       </c>
       <c r="K66" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D66,BIO!A:A,0),2)</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L66" s="15">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M66" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D66,'BIO WAHYU'!B:B,0),4)</f>
@@ -4932,11 +4934,11 @@
       </c>
       <c r="K72" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D72,BIO!A:A,0),2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L72" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D72,'BIO WAHYU'!B:B,0),4)</f>
@@ -4981,11 +4983,11 @@
       </c>
       <c r="K73" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D73,BIO!A:A,0),2)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L73" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M73" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D73,'BIO WAHYU'!B:B,0),4)</f>
@@ -5030,11 +5032,11 @@
       </c>
       <c r="K74" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D74,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D74,'BIO WAHYU'!B:B,0),4)</f>
@@ -5128,11 +5130,11 @@
       </c>
       <c r="K76" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D76,BIO!A:A,0),2)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L76" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M76" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D76,'BIO WAHYU'!B:B,0),4)</f>
@@ -5324,7 +5326,7 @@
       </c>
       <c r="K80" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D80,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="15">
         <f t="shared" si="1"/>
@@ -5373,11 +5375,11 @@
       </c>
       <c r="K81" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D81,BIO!A:A,0),2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D81,'BIO WAHYU'!B:B,0),4)</f>
@@ -5667,11 +5669,11 @@
       </c>
       <c r="K87" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D87,BIO!A:A,0),2)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L87" s="15">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M87" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D87,'BIO WAHYU'!B:B,0),4)</f>
@@ -6059,11 +6061,11 @@
       </c>
       <c r="K95" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D95,BIO!A:A,0),2)</f>
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L95" s="15">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="M95" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D95,'BIO WAHYU'!B:B,0),4)</f>
@@ -6157,11 +6159,11 @@
       </c>
       <c r="K97" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D97,BIO!A:A,0),2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L97" s="15">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M97" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D97,'BIO WAHYU'!B:B,0),4)</f>
@@ -6255,11 +6257,11 @@
       </c>
       <c r="K99" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D99,BIO!A:A,0),2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L99" s="15">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M99" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D99,'BIO WAHYU'!B:B,0),4)</f>
@@ -6304,11 +6306,11 @@
       </c>
       <c r="K100" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D100,BIO!A:A,0),2)</f>
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L100" s="15">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="M100" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D100,'BIO WAHYU'!B:B,0),4)</f>
@@ -6353,11 +6355,11 @@
       </c>
       <c r="K101" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D101,BIO!A:A,0),2)</f>
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L101" s="15">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M101" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D101,'BIO WAHYU'!B:B,0),4)</f>
@@ -6549,11 +6551,11 @@
       </c>
       <c r="K105" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D105,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D105,'BIO WAHYU'!B:B,0),4)</f>
@@ -6696,11 +6698,11 @@
       </c>
       <c r="K108" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D108,BIO!A:A,0),2)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L108" s="15">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M108" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D108,'BIO WAHYU'!B:B,0),4)</f>
@@ -6745,11 +6747,11 @@
       </c>
       <c r="K109" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D109,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D109,'BIO WAHYU'!B:B,0),4)</f>
@@ -6794,11 +6796,11 @@
       </c>
       <c r="K110" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D110,BIO!A:A,0),2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L110" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M110" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D110,'BIO WAHYU'!B:B,0),4)</f>
@@ -6843,7 +6845,7 @@
       </c>
       <c r="K111" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D111,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="15">
         <f t="shared" si="1"/>
@@ -6892,11 +6894,11 @@
       </c>
       <c r="K112" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D112,BIO!A:A,0),2)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L112" s="15">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M112" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D112,'BIO WAHYU'!B:B,0),4)</f>
@@ -6941,11 +6943,11 @@
       </c>
       <c r="K113" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D113,BIO!A:A,0),2)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L113" s="15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M113" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D113,'BIO WAHYU'!B:B,0),4)</f>
@@ -7039,11 +7041,11 @@
       </c>
       <c r="K115" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D115,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L115" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M115" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D115,'BIO WAHYU'!B:B,0),4)</f>
@@ -7088,11 +7090,11 @@
       </c>
       <c r="K116" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D116,BIO!A:A,0),2)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L116" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M116" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D116,'BIO WAHYU'!B:B,0),4)</f>
@@ -7186,7 +7188,7 @@
       </c>
       <c r="K118" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D118,BIO!A:A,0),2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="15">
         <f t="shared" si="1"/>
@@ -7382,11 +7384,11 @@
       </c>
       <c r="K122" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D122,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D122,'BIO WAHYU'!B:B,0),4)</f>
@@ -7431,11 +7433,11 @@
       </c>
       <c r="K123" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D123,BIO!A:A,0),2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L123" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D123,'BIO WAHYU'!B:B,0),4)</f>
@@ -7480,11 +7482,11 @@
       </c>
       <c r="K124" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D124,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M124" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D124,'BIO WAHYU'!B:B,0),4)</f>
@@ -7578,11 +7580,11 @@
       </c>
       <c r="K126" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D126,BIO!A:A,0),2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M126" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D126,'BIO WAHYU'!B:B,0),4)</f>
@@ -7970,11 +7972,11 @@
       </c>
       <c r="K134" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D134,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L134" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D134,'BIO WAHYU'!B:B,0),4)</f>
@@ -8117,7 +8119,7 @@
       </c>
       <c r="K137" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D137,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="15">
         <f t="shared" si="2"/>
@@ -8215,11 +8217,11 @@
       </c>
       <c r="K139" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D139,BIO!A:A,0),2)</f>
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L139" s="15">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M139" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D139,'BIO WAHYU'!B:B,0),4)</f>
@@ -8264,11 +8266,11 @@
       </c>
       <c r="K140" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D140,BIO!A:A,0),2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L140" s="15">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M140" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D140,'BIO WAHYU'!B:B,0),4)</f>
@@ -8362,11 +8364,11 @@
       </c>
       <c r="K142" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D142,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D142,'BIO WAHYU'!B:B,0),4)</f>
@@ -8460,11 +8462,11 @@
       </c>
       <c r="K144" s="14">
         <f>INDEX(BIO!A:E,MATCH(DATA!D144,BIO!A:A,0),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="14">
         <f>INDEX('BIO WAHYU'!B:E,MATCH(DATA!D144,'BIO WAHYU'!B:B,0),4)</f>
@@ -8577,6 +8579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A456D1-6F14-4AB3-B1E2-1E97523234D2}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8585,6 +8588,7 @@
     <col min="3" max="3" width="19.42578125" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8674,6 +8678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29F7AAF-1FE9-4AA8-8261-C5E7933640AD}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8702,7 +8707,8 @@
         <v>240713</v>
       </c>
       <c r="B2" s="14">
-        <v>1</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A2,'BIO WAHYU'!B:B,0),6)</f>
+        <v>4</v>
       </c>
       <c r="C2">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A2,'BIO WAHYU'!B:B,0),5)</f>
@@ -8718,7 +8724,8 @@
         <v>12331450</v>
       </c>
       <c r="B3" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A3,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C3">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A3,'BIO WAHYU'!B:B,0),5)</f>
@@ -8734,6 +8741,7 @@
         <v>292836</v>
       </c>
       <c r="B4" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A4,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C4">
@@ -8750,7 +8758,8 @@
         <v>12321243</v>
       </c>
       <c r="B5" s="14">
-        <v>90</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A5,'BIO WAHYU'!B:B,0),6)</f>
+        <v>88</v>
       </c>
       <c r="C5">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A5,'BIO WAHYU'!B:B,0),5)</f>
@@ -8769,6 +8778,7 @@
         <v>12320853</v>
       </c>
       <c r="B6" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A6,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C6">
@@ -8785,6 +8795,7 @@
         <v>501860</v>
       </c>
       <c r="B7" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A7,'BIO WAHYU'!B:B,0),6)</f>
         <v>3</v>
       </c>
       <c r="C7">
@@ -8801,7 +8812,8 @@
         <v>12322483</v>
       </c>
       <c r="B8" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A8,'BIO WAHYU'!B:B,0),6)</f>
+        <v>1</v>
       </c>
       <c r="C8">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A8,'BIO WAHYU'!B:B,0),5)</f>
@@ -8817,7 +8829,8 @@
         <v>503354</v>
       </c>
       <c r="B9" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A9,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C9">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A9,'BIO WAHYU'!B:B,0),5)</f>
@@ -8836,6 +8849,7 @@
         <v>524283</v>
       </c>
       <c r="B10" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A10,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C10">
@@ -8852,6 +8866,7 @@
         <v>569298</v>
       </c>
       <c r="B11" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A11,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C11">
@@ -8868,6 +8883,7 @@
         <v>481857</v>
       </c>
       <c r="B12" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A12,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C12">
@@ -8884,6 +8900,7 @@
         <v>558955</v>
       </c>
       <c r="B13" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A13,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C13">
@@ -8900,6 +8917,7 @@
         <v>12323218</v>
       </c>
       <c r="B14" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A14,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C14">
@@ -8916,6 +8934,7 @@
         <v>501643</v>
       </c>
       <c r="B15" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A15,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C15">
@@ -8932,6 +8951,7 @@
         <v>408290</v>
       </c>
       <c r="B16" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A16,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C16">
@@ -8948,7 +8968,8 @@
         <v>12326313</v>
       </c>
       <c r="B17" s="14">
-        <v>1</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A17,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C17">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A17,'BIO WAHYU'!B:B,0),5)</f>
@@ -8964,6 +8985,7 @@
         <v>228872</v>
       </c>
       <c r="B18" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A18,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C18">
@@ -8980,6 +9002,7 @@
         <v>12332670</v>
       </c>
       <c r="B19" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A19,'BIO WAHYU'!B:B,0),6)</f>
         <v>5</v>
       </c>
       <c r="C19">
@@ -8996,6 +9019,7 @@
         <v>543771</v>
       </c>
       <c r="B20" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A20,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C20">
@@ -9012,6 +9036,7 @@
         <v>12322237</v>
       </c>
       <c r="B21" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A21,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C21">
@@ -9028,7 +9053,8 @@
         <v>483240</v>
       </c>
       <c r="B22" s="14">
-        <v>1</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A22,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C22">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A22,'BIO WAHYU'!B:B,0),5)</f>
@@ -9044,6 +9070,7 @@
         <v>510295</v>
       </c>
       <c r="B23" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A23,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C23">
@@ -9060,6 +9087,7 @@
         <v>12295717</v>
       </c>
       <c r="B24" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A24,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C24">
@@ -9076,6 +9104,7 @@
         <v>12317091</v>
       </c>
       <c r="B25" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A25,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C25">
@@ -9092,7 +9121,8 @@
         <v>195514</v>
       </c>
       <c r="B26" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A26,'BIO WAHYU'!B:B,0),6)</f>
+        <v>3</v>
       </c>
       <c r="C26">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A26,'BIO WAHYU'!B:B,0),5)</f>
@@ -9108,6 +9138,7 @@
         <v>560814</v>
       </c>
       <c r="B27" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A27,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C27">
@@ -9124,7 +9155,8 @@
         <v>98</v>
       </c>
       <c r="B28" s="14">
-        <v>34</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A28,'BIO WAHYU'!B:B,0),6)</f>
+        <v>36</v>
       </c>
       <c r="C28">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A28,'BIO WAHYU'!B:B,0),5)</f>
@@ -9140,6 +9172,7 @@
         <v>12332811</v>
       </c>
       <c r="B29" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A29,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C29">
@@ -9156,6 +9189,7 @@
         <v>12326533</v>
       </c>
       <c r="B30" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A30,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C30">
@@ -9172,6 +9206,7 @@
         <v>100</v>
       </c>
       <c r="B31" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A31,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C31">
@@ -9188,7 +9223,8 @@
         <v>126952</v>
       </c>
       <c r="B32" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A32,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C32">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A32,'BIO WAHYU'!B:B,0),5)</f>
@@ -9204,7 +9240,8 @@
         <v>530345</v>
       </c>
       <c r="B33" s="14">
-        <v>1</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A33,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C33">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A33,'BIO WAHYU'!B:B,0),5)</f>
@@ -9220,6 +9257,7 @@
         <v>523935</v>
       </c>
       <c r="B34" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A34,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C34">
@@ -9236,6 +9274,7 @@
         <v>501263</v>
       </c>
       <c r="B35" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A35,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C35">
@@ -9252,6 +9291,7 @@
         <v>510299</v>
       </c>
       <c r="B36" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A36,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C36">
@@ -9268,6 +9308,7 @@
         <v>10466</v>
       </c>
       <c r="B37" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A37,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C37">
@@ -9284,6 +9325,7 @@
         <v>1661</v>
       </c>
       <c r="B38" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A38,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C38">
@@ -9300,6 +9342,7 @@
         <v>523430</v>
       </c>
       <c r="B39" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A39,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C39">
@@ -9316,7 +9359,8 @@
         <v>127198</v>
       </c>
       <c r="B40" s="14">
-        <v>14</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A40,'BIO WAHYU'!B:B,0),6)</f>
+        <v>18</v>
       </c>
       <c r="C40">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A40,'BIO WAHYU'!B:B,0),5)</f>
@@ -9332,6 +9376,7 @@
         <v>571174</v>
       </c>
       <c r="B41" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A41,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C41">
@@ -9348,6 +9393,7 @@
         <v>416191</v>
       </c>
       <c r="B42" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A42,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C42">
@@ -9364,7 +9410,8 @@
         <v>12295592</v>
       </c>
       <c r="B43" s="14">
-        <v>10</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A43,'BIO WAHYU'!B:B,0),6)</f>
+        <v>11</v>
       </c>
       <c r="C43">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A43,'BIO WAHYU'!B:B,0),5)</f>
@@ -9380,6 +9427,7 @@
         <v>510053</v>
       </c>
       <c r="B44" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A44,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C44">
@@ -9396,7 +9444,8 @@
         <v>503866</v>
       </c>
       <c r="B45" s="14">
-        <v>2</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A45,'BIO WAHYU'!B:B,0),6)</f>
+        <v>4</v>
       </c>
       <c r="C45">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A45,'BIO WAHYU'!B:B,0),5)</f>
@@ -9412,6 +9461,7 @@
         <v>524281</v>
       </c>
       <c r="B46" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A46,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C46">
@@ -9428,6 +9478,7 @@
         <v>12295833</v>
       </c>
       <c r="B47" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A47,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C47">
@@ -9444,7 +9495,8 @@
         <v>240048</v>
       </c>
       <c r="B48" s="14">
-        <v>2</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A48,'BIO WAHYU'!B:B,0),6)</f>
+        <v>1</v>
       </c>
       <c r="C48">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A48,'BIO WAHYU'!B:B,0),5)</f>
@@ -9460,6 +9512,7 @@
         <v>246732</v>
       </c>
       <c r="B49" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A49,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C49">
@@ -9476,7 +9529,8 @@
         <v>530334</v>
       </c>
       <c r="B50" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A50,'BIO WAHYU'!B:B,0),6)</f>
+        <v>1</v>
       </c>
       <c r="C50">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A50,'BIO WAHYU'!B:B,0),5)</f>
@@ -9492,7 +9546,8 @@
         <v>211794</v>
       </c>
       <c r="B51" s="14">
-        <v>2</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A51,'BIO WAHYU'!B:B,0),6)</f>
+        <v>3</v>
       </c>
       <c r="C51">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A51,'BIO WAHYU'!B:B,0),5)</f>
@@ -9508,7 +9563,8 @@
         <v>535790</v>
       </c>
       <c r="B52" s="14">
-        <v>3</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A52,'BIO WAHYU'!B:B,0),6)</f>
+        <v>4</v>
       </c>
       <c r="C52">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A52,'BIO WAHYU'!B:B,0),5)</f>
@@ -9524,6 +9580,7 @@
         <v>62086</v>
       </c>
       <c r="B53" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A53,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C53">
@@ -9540,7 +9597,8 @@
         <v>116871</v>
       </c>
       <c r="B54" s="14">
-        <v>5</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A54,'BIO WAHYU'!B:B,0),6)</f>
+        <v>8</v>
       </c>
       <c r="C54">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A54,'BIO WAHYU'!B:B,0),5)</f>
@@ -9556,6 +9614,7 @@
         <v>304264</v>
       </c>
       <c r="B55" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A55,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C55">
@@ -9572,6 +9631,7 @@
         <v>549259</v>
       </c>
       <c r="B56" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A56,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C56">
@@ -9588,6 +9648,7 @@
         <v>523938</v>
       </c>
       <c r="B57" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A57,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C57">
@@ -9604,6 +9665,7 @@
         <v>523849</v>
       </c>
       <c r="B58" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A58,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C58">
@@ -9620,6 +9682,7 @@
         <v>12295826</v>
       </c>
       <c r="B59" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A59,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C59">
@@ -9636,6 +9699,7 @@
         <v>385575</v>
       </c>
       <c r="B60" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A60,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C60">
@@ -9652,6 +9716,7 @@
         <v>12326920</v>
       </c>
       <c r="B61" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A61,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C61">
@@ -9668,6 +9733,7 @@
         <v>484741</v>
       </c>
       <c r="B62" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A62,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C62">
@@ -9684,6 +9750,7 @@
         <v>12327316</v>
       </c>
       <c r="B63" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A63,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C63">
@@ -9700,7 +9767,8 @@
         <v>12334635</v>
       </c>
       <c r="B64" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A64,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C64">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A64,'BIO WAHYU'!B:B,0),5)</f>
@@ -9716,6 +9784,7 @@
         <v>12326118</v>
       </c>
       <c r="B65" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A65,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C65">
@@ -9732,6 +9801,7 @@
         <v>345427</v>
       </c>
       <c r="B66" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A66,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C66">
@@ -9748,6 +9818,7 @@
         <v>499483</v>
       </c>
       <c r="B67" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A67,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C67">
@@ -9764,7 +9835,8 @@
         <v>195918</v>
       </c>
       <c r="B68" s="14">
-        <v>4</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A68,'BIO WAHYU'!B:B,0),6)</f>
+        <v>5</v>
       </c>
       <c r="C68">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A68,'BIO WAHYU'!B:B,0),5)</f>
@@ -9780,6 +9852,7 @@
         <v>126951</v>
       </c>
       <c r="B69" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A69,'BIO WAHYU'!B:B,0),6)</f>
         <v>3</v>
       </c>
       <c r="C69">
@@ -9796,6 +9869,7 @@
         <v>63887</v>
       </c>
       <c r="B70" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A70,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C70">
@@ -9812,7 +9886,8 @@
         <v>229765</v>
       </c>
       <c r="B71" s="14">
-        <v>21</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A71,'BIO WAHYU'!B:B,0),6)</f>
+        <v>26</v>
       </c>
       <c r="C71">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A71,'BIO WAHYU'!B:B,0),5)</f>
@@ -9828,7 +9903,8 @@
         <v>574633</v>
       </c>
       <c r="B72" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A72,'BIO WAHYU'!B:B,0),6)</f>
+        <v>1</v>
       </c>
       <c r="C72">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A72,'BIO WAHYU'!B:B,0),5)</f>
@@ -9844,6 +9920,7 @@
         <v>61688</v>
       </c>
       <c r="B73" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A73,'BIO WAHYU'!B:B,0),6)</f>
         <v>4</v>
       </c>
       <c r="C73">
@@ -9860,6 +9937,7 @@
         <v>104</v>
       </c>
       <c r="B74" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A74,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C74">
@@ -9876,6 +9954,7 @@
         <v>12295724</v>
       </c>
       <c r="B75" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A75,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C75">
@@ -9892,6 +9971,7 @@
         <v>12325263</v>
       </c>
       <c r="B76" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A76,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C76">
@@ -9908,6 +9988,7 @@
         <v>12324194</v>
       </c>
       <c r="B77" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A77,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C77">
@@ -9924,6 +10005,7 @@
         <v>486638</v>
       </c>
       <c r="B78" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A78,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C78">
@@ -9940,6 +10022,7 @@
         <v>530058</v>
       </c>
       <c r="B79" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A79,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C79">
@@ -9956,6 +10039,7 @@
         <v>231278</v>
       </c>
       <c r="B80" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A80,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C80">
@@ -9972,7 +10056,8 @@
         <v>199217</v>
       </c>
       <c r="B81" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A81,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C81">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A81,'BIO WAHYU'!B:B,0),5)</f>
@@ -9988,6 +10073,7 @@
         <v>222816</v>
       </c>
       <c r="B82" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A82,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C82">
@@ -10004,7 +10090,8 @@
         <v>342829</v>
       </c>
       <c r="B83" s="14">
-        <v>1</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A83,'BIO WAHYU'!B:B,0),6)</f>
+        <v>0</v>
       </c>
       <c r="C83">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A83,'BIO WAHYU'!B:B,0),5)</f>
@@ -10020,7 +10107,8 @@
         <v>543826</v>
       </c>
       <c r="B84" s="14">
-        <v>23</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A84,'BIO WAHYU'!B:B,0),6)</f>
+        <v>28</v>
       </c>
       <c r="C84">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A84,'BIO WAHYU'!B:B,0),5)</f>
@@ -10036,6 +10124,7 @@
         <v>160</v>
       </c>
       <c r="B85" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A85,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C85">
@@ -10052,6 +10141,7 @@
         <v>287622</v>
       </c>
       <c r="B86" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A86,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C86">
@@ -10068,6 +10158,7 @@
         <v>542823</v>
       </c>
       <c r="B87" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A87,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C87">
@@ -10084,6 +10175,7 @@
         <v>12295887</v>
       </c>
       <c r="B88" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A88,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C88">
@@ -10100,7 +10192,8 @@
         <v>12333237</v>
       </c>
       <c r="B89" s="14">
-        <v>8</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A89,'BIO WAHYU'!B:B,0),6)</f>
+        <v>11</v>
       </c>
       <c r="C89">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A89,'BIO WAHYU'!B:B,0),5)</f>
@@ -10116,7 +10209,8 @@
         <v>477625</v>
       </c>
       <c r="B90" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A90,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C90">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A90,'BIO WAHYU'!B:B,0),5)</f>
@@ -10132,6 +10226,7 @@
         <v>12295980</v>
       </c>
       <c r="B91" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A91,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C91">
@@ -10148,6 +10243,7 @@
         <v>12295626</v>
       </c>
       <c r="B92" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A92,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C92">
@@ -10164,7 +10260,8 @@
         <v>126963</v>
       </c>
       <c r="B93" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A93,'BIO WAHYU'!B:B,0),6)</f>
+        <v>1</v>
       </c>
       <c r="C93">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A93,'BIO WAHYU'!B:B,0),5)</f>
@@ -10180,6 +10277,7 @@
         <v>199007</v>
       </c>
       <c r="B94" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A94,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C94">
@@ -10196,6 +10294,7 @@
         <v>12295536</v>
       </c>
       <c r="B95" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A95,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C95">
@@ -10212,7 +10311,8 @@
         <v>213944</v>
       </c>
       <c r="B96" s="14">
-        <v>4</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A96,'BIO WAHYU'!B:B,0),6)</f>
+        <v>7</v>
       </c>
       <c r="C96">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A96,'BIO WAHYU'!B:B,0),5)</f>
@@ -10228,6 +10328,7 @@
         <v>278608</v>
       </c>
       <c r="B97" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A97,'BIO WAHYU'!B:B,0),6)</f>
         <v>4</v>
       </c>
       <c r="C97">
@@ -10244,7 +10345,8 @@
         <v>12323463</v>
       </c>
       <c r="B98" s="14">
-        <v>91</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A98,'BIO WAHYU'!B:B,0),6)</f>
+        <v>88</v>
       </c>
       <c r="C98">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A98,'BIO WAHYU'!B:B,0),5)</f>
@@ -10260,7 +10362,8 @@
         <v>12321241</v>
       </c>
       <c r="B99" s="14">
-        <v>21</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A99,'BIO WAHYU'!B:B,0),6)</f>
+        <v>31</v>
       </c>
       <c r="C99">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A99,'BIO WAHYU'!B:B,0),5)</f>
@@ -10276,6 +10379,7 @@
         <v>287403</v>
       </c>
       <c r="B100" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A100,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C100">
@@ -10292,6 +10396,7 @@
         <v>102</v>
       </c>
       <c r="B101" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A101,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C101">
@@ -10308,6 +10413,7 @@
         <v>511584</v>
       </c>
       <c r="B102" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A102,'BIO WAHYU'!B:B,0),6)</f>
         <v>3</v>
       </c>
       <c r="C102">
@@ -10324,6 +10430,7 @@
         <v>12295542</v>
       </c>
       <c r="B103" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A103,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C103">
@@ -10340,7 +10447,8 @@
         <v>546446</v>
       </c>
       <c r="B104" s="14">
-        <v>2</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A104,'BIO WAHYU'!B:B,0),6)</f>
+        <v>3</v>
       </c>
       <c r="C104">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A104,'BIO WAHYU'!B:B,0),5)</f>
@@ -10356,6 +10464,7 @@
         <v>199020</v>
       </c>
       <c r="B105" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A105,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C105">
@@ -10372,6 +10481,7 @@
         <v>522623</v>
       </c>
       <c r="B106" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A106,'BIO WAHYU'!B:B,0),6)</f>
         <v>10</v>
       </c>
       <c r="C106">
@@ -10388,6 +10498,7 @@
         <v>12303072</v>
       </c>
       <c r="B107" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A107,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C107">
@@ -10404,6 +10515,7 @@
         <v>12295820</v>
       </c>
       <c r="B108" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A108,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C108">
@@ -10420,6 +10532,7 @@
         <v>358231</v>
       </c>
       <c r="B109" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A109,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C109">
@@ -10436,6 +10549,7 @@
         <v>396176</v>
       </c>
       <c r="B110" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A110,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C110">
@@ -10452,6 +10566,7 @@
         <v>539088</v>
       </c>
       <c r="B111" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A111,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C111">
@@ -10468,6 +10583,7 @@
         <v>525590</v>
       </c>
       <c r="B112" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A112,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C112">
@@ -10484,6 +10600,7 @@
         <v>368809</v>
       </c>
       <c r="B113" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A113,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C113">
@@ -10500,6 +10617,7 @@
         <v>199010</v>
       </c>
       <c r="B114" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A114,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C114">
@@ -10516,6 +10634,7 @@
         <v>519286</v>
       </c>
       <c r="B115" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A115,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C115">
@@ -10532,6 +10651,7 @@
         <v>523194</v>
       </c>
       <c r="B116" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A116,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C116">
@@ -10548,6 +10668,7 @@
         <v>61690</v>
       </c>
       <c r="B117" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A117,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C117">
@@ -10564,6 +10685,7 @@
         <v>12312295</v>
       </c>
       <c r="B118" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A118,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C118">
@@ -10580,7 +10702,8 @@
         <v>12318079</v>
       </c>
       <c r="B119" s="14">
-        <v>3</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A119,'BIO WAHYU'!B:B,0),6)</f>
+        <v>4</v>
       </c>
       <c r="C119">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A119,'BIO WAHYU'!B:B,0),5)</f>
@@ -10596,7 +10719,8 @@
         <v>12321230</v>
       </c>
       <c r="B120" s="14">
-        <v>2</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A120,'BIO WAHYU'!B:B,0),6)</f>
+        <v>3</v>
       </c>
       <c r="C120">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A120,'BIO WAHYU'!B:B,0),5)</f>
@@ -10612,7 +10736,8 @@
         <v>12301356</v>
       </c>
       <c r="B121" s="14">
-        <v>3</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A121,'BIO WAHYU'!B:B,0),6)</f>
+        <v>5</v>
       </c>
       <c r="C121">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A121,'BIO WAHYU'!B:B,0),5)</f>
@@ -10628,6 +10753,7 @@
         <v>12295752</v>
       </c>
       <c r="B122" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A122,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C122">
@@ -10644,7 +10770,8 @@
         <v>12313881</v>
       </c>
       <c r="B123" s="14">
-        <v>20</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A123,'BIO WAHYU'!B:B,0),6)</f>
+        <v>28</v>
       </c>
       <c r="C123">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A123,'BIO WAHYU'!B:B,0),5)</f>
@@ -10660,6 +10787,7 @@
         <v>12302808</v>
       </c>
       <c r="B124" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A124,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C124">
@@ -10676,7 +10804,8 @@
         <v>12334637</v>
       </c>
       <c r="B125" s="14">
-        <v>2</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A125,'BIO WAHYU'!B:B,0),6)</f>
+        <v>3</v>
       </c>
       <c r="C125">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A125,'BIO WAHYU'!B:B,0),5)</f>
@@ -10692,7 +10821,8 @@
         <v>471389</v>
       </c>
       <c r="B126" s="14">
-        <v>1</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A126,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C126">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A126,'BIO WAHYU'!B:B,0),5)</f>
@@ -10708,7 +10838,8 @@
         <v>529249</v>
       </c>
       <c r="B127" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A127,'BIO WAHYU'!B:B,0),6)</f>
+        <v>1</v>
       </c>
       <c r="C127">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A127,'BIO WAHYU'!B:B,0),5)</f>
@@ -10724,7 +10855,8 @@
         <v>366702</v>
       </c>
       <c r="B128" s="14">
-        <v>2</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A128,'BIO WAHYU'!B:B,0),6)</f>
+        <v>1</v>
       </c>
       <c r="C128">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A128,'BIO WAHYU'!B:B,0),5)</f>
@@ -10740,7 +10872,8 @@
         <v>514589</v>
       </c>
       <c r="B129" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A129,'BIO WAHYU'!B:B,0),6)</f>
+        <v>2</v>
       </c>
       <c r="C129">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A129,'BIO WAHYU'!B:B,0),5)</f>
@@ -10756,7 +10889,8 @@
         <v>401031</v>
       </c>
       <c r="B130" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A130,'BIO WAHYU'!B:B,0),6)</f>
+        <v>1</v>
       </c>
       <c r="C130">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A130,'BIO WAHYU'!B:B,0),5)</f>
@@ -10772,7 +10906,8 @@
         <v>562953</v>
       </c>
       <c r="B131" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A131,'BIO WAHYU'!B:B,0),6)</f>
+        <v>1</v>
       </c>
       <c r="C131">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A131,'BIO WAHYU'!B:B,0),5)</f>
@@ -10788,6 +10923,7 @@
         <v>529090</v>
       </c>
       <c r="B132" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A132,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C132">
@@ -10804,6 +10940,7 @@
         <v>345691</v>
       </c>
       <c r="B133" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A133,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C133">
@@ -10820,6 +10957,7 @@
         <v>347538</v>
       </c>
       <c r="B134" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A134,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C134">
@@ -10836,6 +10974,7 @@
         <v>301600</v>
       </c>
       <c r="B135" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A135,'BIO WAHYU'!B:B,0),6)</f>
         <v>2</v>
       </c>
       <c r="C135">
@@ -10852,6 +10991,7 @@
         <v>563095</v>
       </c>
       <c r="B136" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A136,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C136">
@@ -10868,7 +11008,8 @@
         <v>480658</v>
       </c>
       <c r="B137" s="14">
-        <v>2</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A137,'BIO WAHYU'!B:B,0),6)</f>
+        <v>5</v>
       </c>
       <c r="C137">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A137,'BIO WAHYU'!B:B,0),5)</f>
@@ -10884,6 +11025,7 @@
         <v>543720</v>
       </c>
       <c r="B138" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A138,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C138">
@@ -10900,6 +11042,7 @@
         <v>352167</v>
       </c>
       <c r="B139" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A139,'BIO WAHYU'!B:B,0),6)</f>
         <v>1</v>
       </c>
       <c r="C139">
@@ -10916,6 +11059,7 @@
         <v>526916</v>
       </c>
       <c r="B140" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A140,'BIO WAHYU'!B:B,0),6)</f>
         <v>3</v>
       </c>
       <c r="C140">
@@ -10932,6 +11076,7 @@
         <v>491288</v>
       </c>
       <c r="B141" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A141,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C141">
@@ -10948,6 +11093,7 @@
         <v>501141</v>
       </c>
       <c r="B142" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A142,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C142">
@@ -10964,7 +11110,8 @@
         <v>240084</v>
       </c>
       <c r="B143" s="14">
-        <v>0</v>
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A143,'BIO WAHYU'!B:B,0),6)</f>
+        <v>3</v>
       </c>
       <c r="C143">
         <f>INDEX('BIO WAHYU'!B:F,MATCH(BIO!A143,'BIO WAHYU'!B:B,0),5)</f>
@@ -10980,6 +11127,7 @@
         <v>12324647</v>
       </c>
       <c r="B144" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A144,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C144">
@@ -10996,6 +11144,7 @@
         <v>503633</v>
       </c>
       <c r="B145" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A145,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C145">
@@ -11012,6 +11161,7 @@
         <v>12322430</v>
       </c>
       <c r="B146" s="14">
+        <f>INDEX('BIO WAHYU'!B:G,MATCH(BIO!A146,'BIO WAHYU'!B:B,0),6)</f>
         <v>0</v>
       </c>
       <c r="C146">
@@ -11030,6 +11180,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20CE5235-A8E0-42AF-8D8D-5D5BD306AC0F}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13093,6 +13244,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19CFB2D-1CEE-48C0-A9E8-35B42FA19955}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14747,7 +14899,8 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F42E2FEA-7579-4105-BB5C-707DD11104C2}">
-  <dimension ref="A1:N146"/>
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:N191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -14810,7 +14963,7 @@
       </c>
       <c r="D2" s="27">
         <f t="shared" ref="D2:D65" si="0">IF(G2&gt;0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="28">
         <v>1</v>
@@ -14819,7 +14972,8 @@
         <v>1</v>
       </c>
       <c r="G2" s="44">
-        <v>0</v>
+        <f>J2</f>
+        <v>1</v>
       </c>
       <c r="H2" s="28">
         <f t="shared" ref="H2:H65" si="1">MAX(G2-F2,0)</f>
@@ -14830,19 +14984,19 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <f>INDEX(M:N,MATCH(B2,M:M,0),2)</f>
+        <f>_xlfn.IFNA(INDEX(M:N,MATCH(B2,M:M,0),2),0)</f>
         <v>1</v>
       </c>
       <c r="K2" s="38">
         <f>G2-J2</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="38"/>
-      <c r="M2" s="9">
-        <v>240713</v>
-      </c>
-      <c r="N2" s="14">
-        <v>1</v>
+      <c r="M2">
+        <v>543826</v>
+      </c>
+      <c r="N2">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -14866,30 +15020,31 @@
         <v>1</v>
       </c>
       <c r="G3" s="44">
-        <v>7</v>
+        <f t="shared" ref="G3:G66" si="2">J3</f>
+        <v>11</v>
       </c>
       <c r="H3" s="28">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I66" si="2">IF(G3&gt;=3,1,0)</f>
+        <f t="shared" ref="I3:I66" si="3">IF(G3&gt;=3,1,0)</f>
         <v>1</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J66" si="3">INDEX(M:N,MATCH(B3,M:M,0),2)</f>
-        <v>10</v>
+        <f t="shared" ref="J3:J66" si="4">_xlfn.IFNA(INDEX(M:N,MATCH(B3,M:M,0),2),0)</f>
+        <v>11</v>
       </c>
       <c r="K3" s="38">
-        <f t="shared" ref="K3:K66" si="4">G3-J3</f>
-        <v>-3</v>
+        <f t="shared" ref="K3:K66" si="5">G3-J3</f>
+        <v>0</v>
       </c>
       <c r="L3" s="38"/>
-      <c r="M3" s="9">
-        <v>12331450</v>
-      </c>
-      <c r="N3" s="14">
-        <v>0</v>
+      <c r="M3">
+        <v>12313881</v>
+      </c>
+      <c r="N3">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -14913,6 +15068,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H4" s="28">
@@ -14920,23 +15076,23 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K4" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L4" s="38"/>
-      <c r="M4" s="9">
-        <v>292836</v>
-      </c>
-      <c r="N4" s="14">
-        <v>0</v>
+      <c r="M4">
+        <v>61688</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -14951,7 +15107,7 @@
       </c>
       <c r="D5" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="28">
         <v>2</v>
@@ -14960,30 +15116,31 @@
         <v>1</v>
       </c>
       <c r="G5" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H5" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K5" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L5" s="38"/>
-      <c r="M5" s="9">
-        <v>12321243</v>
-      </c>
-      <c r="N5" s="14">
-        <v>90</v>
+      <c r="M5">
+        <v>535790</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -15007,6 +15164,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H6" s="28">
@@ -15014,23 +15172,23 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K6" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L6" s="38"/>
-      <c r="M6" s="9">
-        <v>12320853</v>
-      </c>
-      <c r="N6" s="14">
-        <v>0</v>
+      <c r="M6">
+        <v>240713</v>
+      </c>
+      <c r="N6">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -15054,6 +15212,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H7" s="28">
@@ -15061,23 +15220,23 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K7" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L7" s="38"/>
-      <c r="M7" s="9">
-        <v>501860</v>
-      </c>
-      <c r="N7" s="14">
-        <v>3</v>
+      <c r="M7">
+        <v>12318079</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -15101,6 +15260,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H8" s="28">
@@ -15108,23 +15268,23 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K8" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L8" s="38"/>
-      <c r="M8" s="9">
-        <v>12322483</v>
-      </c>
-      <c r="N8" s="14">
-        <v>0</v>
+      <c r="M8">
+        <v>503866</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15148,6 +15308,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H9" s="28">
@@ -15155,23 +15316,23 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K9" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L9" s="38"/>
-      <c r="M9" s="9">
-        <v>503354</v>
-      </c>
-      <c r="N9" s="14">
-        <v>0</v>
+      <c r="M9">
+        <v>278608</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -15195,30 +15356,31 @@
         <v>1</v>
       </c>
       <c r="G10" s="44">
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="H10" s="28">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="J10">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="K10" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L10" s="38"/>
-      <c r="M10" s="9">
-        <v>524283</v>
-      </c>
-      <c r="N10" s="14">
-        <v>0</v>
+      <c r="M10">
+        <v>127198</v>
+      </c>
+      <c r="N10">
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -15242,6 +15404,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H11" s="28">
@@ -15249,23 +15412,23 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K11" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L11" s="38"/>
-      <c r="M11" s="9">
-        <v>569298</v>
-      </c>
-      <c r="N11" s="14">
-        <v>0</v>
+      <c r="M11">
+        <v>116871</v>
+      </c>
+      <c r="N11">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -15289,6 +15452,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H12" s="28">
@@ -15296,23 +15460,23 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K12" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L12" s="38"/>
-      <c r="M12" s="9">
-        <v>481857</v>
-      </c>
-      <c r="N12" s="14">
-        <v>0</v>
+      <c r="M12">
+        <v>511584</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -15336,6 +15500,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H13" s="28">
@@ -15343,23 +15508,23 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K13" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L13" s="38"/>
-      <c r="M13" s="9">
-        <v>558955</v>
-      </c>
-      <c r="N13" s="14">
-        <v>0</v>
+      <c r="M13">
+        <v>211794</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -15383,6 +15548,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="44">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H14" s="28">
@@ -15390,23 +15556,23 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="K14" s="38">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L14" s="38"/>
-      <c r="M14" s="9">
-        <v>12323218</v>
-      </c>
-      <c r="N14" s="14">
-        <v>1</v>
+      <c r="M14">
+        <v>126951</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -15430,6 +15596,7 @@
         <v>30</v>
       </c>
       <c r="G15" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H15" s="28">
@@ -15437,23 +15604,23 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K15" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L15" s="38"/>
-      <c r="M15" s="9">
-        <v>501643</v>
-      </c>
-      <c r="N15" s="14">
-        <v>0</v>
+      <c r="M15">
+        <v>12321230</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -15477,6 +15644,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H16" s="28">
@@ -15484,23 +15652,23 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K16" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L16" s="38"/>
-      <c r="M16" s="9">
-        <v>408290</v>
-      </c>
-      <c r="N16" s="14">
-        <v>2</v>
+      <c r="M16">
+        <v>195514</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -15524,6 +15692,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H17" s="28">
@@ -15531,23 +15700,23 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L17" s="38"/>
-      <c r="M17" s="9">
-        <v>12326313</v>
-      </c>
-      <c r="N17" s="14">
-        <v>1</v>
+      <c r="M17">
+        <v>12334637</v>
+      </c>
+      <c r="N17">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -15571,30 +15740,31 @@
         <v>1</v>
       </c>
       <c r="G18" s="44">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="H18" s="28">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J18">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f t="shared" si="4"/>
+        <v>7</v>
       </c>
       <c r="K18" s="38">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L18" s="38"/>
-      <c r="M18" s="9">
-        <v>228872</v>
-      </c>
-      <c r="N18" s="14">
-        <v>0</v>
+      <c r="M18">
+        <v>526916</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -15618,6 +15788,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H19" s="28">
@@ -15625,23 +15796,23 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J19">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="K19" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L19" s="38"/>
-      <c r="M19" s="9">
-        <v>12332670</v>
-      </c>
-      <c r="N19" s="14">
-        <v>5</v>
+      <c r="M19">
+        <v>546446</v>
+      </c>
+      <c r="N19">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -15665,6 +15836,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H20" s="28">
@@ -15672,23 +15844,23 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K20" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L20" s="38"/>
-      <c r="M20" s="9">
-        <v>543771</v>
-      </c>
-      <c r="N20" s="14">
-        <v>0</v>
+      <c r="M20">
+        <v>240084</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -15712,6 +15884,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H21" s="28">
@@ -15719,23 +15892,23 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K21" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L21" s="38"/>
-      <c r="M21" s="9">
-        <v>12322237</v>
-      </c>
-      <c r="N21" s="14">
-        <v>1</v>
+      <c r="M21">
+        <v>501860</v>
+      </c>
+      <c r="N21">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -15750,7 +15923,7 @@
       </c>
       <c r="D22" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="28">
         <v>1</v>
@@ -15759,30 +15932,31 @@
         <v>1</v>
       </c>
       <c r="G22" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="H22" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="K22" s="38">
-        <f t="shared" si="4"/>
-        <v>-2</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L22" s="38"/>
-      <c r="M22" s="9">
-        <v>483240</v>
-      </c>
-      <c r="N22" s="14">
-        <v>1</v>
+      <c r="M22" t="s">
+        <v>98</v>
+      </c>
+      <c r="N22">
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -15797,7 +15971,7 @@
       </c>
       <c r="D23" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="28">
         <v>1</v>
@@ -15806,30 +15980,31 @@
         <v>1</v>
       </c>
       <c r="G23" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="H23" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="K23" s="38">
-        <f t="shared" si="4"/>
-        <v>-2</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L23" s="38"/>
-      <c r="M23" s="9">
-        <v>510295</v>
-      </c>
-      <c r="N23" s="14">
-        <v>0</v>
+      <c r="M23">
+        <v>12321243</v>
+      </c>
+      <c r="N23">
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -15853,6 +16028,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H24" s="28">
@@ -15860,23 +16036,23 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K24" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L24" s="38"/>
-      <c r="M24" s="9">
-        <v>12295717</v>
-      </c>
-      <c r="N24" s="14">
-        <v>1</v>
+      <c r="M24">
+        <v>12323463</v>
+      </c>
+      <c r="N24">
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -15900,6 +16076,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H25" s="28">
@@ -15907,23 +16084,23 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K25" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L25" s="38"/>
-      <c r="M25" s="9">
-        <v>12317091</v>
-      </c>
-      <c r="N25" s="14">
-        <v>0</v>
+      <c r="M25">
+        <v>12321241</v>
+      </c>
+      <c r="N25">
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -15947,6 +16124,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H26" s="28">
@@ -15954,23 +16132,23 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K26" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L26" s="38"/>
-      <c r="M26" s="9">
-        <v>195514</v>
-      </c>
-      <c r="N26" s="14">
-        <v>0</v>
+      <c r="M26">
+        <v>229765</v>
+      </c>
+      <c r="N26">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -15994,30 +16172,31 @@
         <v>1</v>
       </c>
       <c r="G27" s="44">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="H27" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="K27" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L27" s="38"/>
-      <c r="M27" s="9">
-        <v>560814</v>
-      </c>
-      <c r="N27" s="14">
-        <v>2</v>
+      <c r="M27">
+        <v>213944</v>
+      </c>
+      <c r="N27">
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -16041,6 +16220,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H28" s="28">
@@ -16048,23 +16228,23 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K28" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L28" s="38"/>
-      <c r="M28" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="N28" s="14">
-        <v>34</v>
+      <c r="M28">
+        <v>199217</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -16088,6 +16268,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H29" s="28">
@@ -16095,23 +16276,23 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K29" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L29" s="38"/>
-      <c r="M29" s="9">
-        <v>12332811</v>
-      </c>
-      <c r="N29" s="14">
-        <v>0</v>
+      <c r="M29">
+        <v>12334635</v>
+      </c>
+      <c r="N29">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -16135,6 +16316,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H30" s="28">
@@ -16142,23 +16324,23 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K30" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L30" s="38"/>
-      <c r="M30" s="9">
-        <v>12326533</v>
-      </c>
-      <c r="N30" s="14">
-        <v>0</v>
+      <c r="M30">
+        <v>499483</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -16182,6 +16364,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H31" s="28">
@@ -16189,22 +16372,22 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K31" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L31" s="38"/>
-      <c r="M31" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="N31" s="14">
+      <c r="M31">
+        <v>12331450</v>
+      </c>
+      <c r="N31">
         <v>2</v>
       </c>
     </row>
@@ -16229,6 +16412,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H32" s="28">
@@ -16236,23 +16420,23 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K32" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L32" s="38"/>
-      <c r="M32" s="9">
+      <c r="M32">
         <v>126952</v>
       </c>
-      <c r="N32" s="14">
-        <v>0</v>
+      <c r="N32">
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -16267,7 +16451,7 @@
       </c>
       <c r="D33" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="28">
         <v>0</v>
@@ -16276,30 +16460,31 @@
         <v>1</v>
       </c>
       <c r="G33" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H33" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K33" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L33" s="38"/>
-      <c r="M33" s="9">
-        <v>530345</v>
-      </c>
-      <c r="N33" s="14">
-        <v>1</v>
+      <c r="M33">
+        <v>12295542</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -16323,30 +16508,31 @@
         <v>1</v>
       </c>
       <c r="G34" s="44">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>10</v>
       </c>
       <c r="H34" s="28">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="K34" s="38">
-        <f t="shared" si="4"/>
-        <v>-5</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L34" s="38"/>
-      <c r="M34" s="9">
-        <v>523935</v>
-      </c>
-      <c r="N34" s="14">
-        <v>0</v>
+      <c r="M34">
+        <v>483240</v>
+      </c>
+      <c r="N34">
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -16370,6 +16556,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H35" s="28">
@@ -16377,23 +16564,23 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K35" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L35" s="38"/>
-      <c r="M35" s="9">
-        <v>501263</v>
-      </c>
-      <c r="N35" s="14">
-        <v>1</v>
+      <c r="M35">
+        <v>560814</v>
+      </c>
+      <c r="N35">
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -16417,6 +16604,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H36" s="28">
@@ -16424,23 +16612,23 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K36" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L36" s="38"/>
-      <c r="M36" s="9">
-        <v>510299</v>
-      </c>
-      <c r="N36" s="14">
-        <v>0</v>
+      <c r="M36" t="s">
+        <v>100</v>
+      </c>
+      <c r="N36">
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -16464,6 +16652,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H37" s="28">
@@ -16471,23 +16660,23 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K37" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L37" s="38"/>
-      <c r="M37" s="9">
-        <v>10466</v>
-      </c>
-      <c r="N37" s="14">
-        <v>1</v>
+      <c r="M37">
+        <v>503354</v>
+      </c>
+      <c r="N37">
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -16511,6 +16700,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H38" s="28">
@@ -16518,23 +16708,23 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K38" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L38" s="38"/>
-      <c r="M38" s="9">
-        <v>1661</v>
-      </c>
-      <c r="N38" s="14">
-        <v>0</v>
+      <c r="M38">
+        <v>12326313</v>
+      </c>
+      <c r="N38">
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -16558,6 +16748,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H39" s="28">
@@ -16565,23 +16756,23 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K39" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L39" s="38"/>
-      <c r="M39" s="9">
-        <v>523430</v>
-      </c>
-      <c r="N39" s="14">
-        <v>0</v>
+      <c r="M39">
+        <v>514589</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -16596,7 +16787,7 @@
       </c>
       <c r="D40" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="28">
         <v>0</v>
@@ -16605,30 +16796,31 @@
         <v>2</v>
       </c>
       <c r="G40" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H40" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K40" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L40" s="38"/>
-      <c r="M40" s="9">
-        <v>127198</v>
-      </c>
-      <c r="N40" s="14">
-        <v>14</v>
+      <c r="M40">
+        <v>542823</v>
+      </c>
+      <c r="N40">
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -16643,7 +16835,7 @@
       </c>
       <c r="D41" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="28">
         <v>3</v>
@@ -16652,30 +16844,31 @@
         <v>1</v>
       </c>
       <c r="G41" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H41" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K41" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L41" s="38"/>
-      <c r="M41" s="9">
-        <v>571174</v>
-      </c>
-      <c r="N41" s="14">
-        <v>0</v>
+      <c r="M41">
+        <v>471389</v>
+      </c>
+      <c r="N41">
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -16699,6 +16892,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="44">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="H42" s="28">
@@ -16706,23 +16900,23 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J42">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>4</v>
       </c>
       <c r="K42" s="38">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L42" s="38"/>
-      <c r="M42" s="9">
-        <v>416191</v>
-      </c>
-      <c r="N42" s="14">
-        <v>0</v>
+      <c r="M42">
+        <v>301600</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -16737,7 +16931,7 @@
       </c>
       <c r="D43" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="28">
         <v>1</v>
@@ -16746,30 +16940,31 @@
         <v>1</v>
       </c>
       <c r="G43" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="H43" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="K43" s="38">
-        <f t="shared" si="4"/>
-        <v>-2</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L43" s="38"/>
-      <c r="M43" s="9">
-        <v>12295592</v>
-      </c>
-      <c r="N43" s="14">
-        <v>10</v>
+      <c r="M43">
+        <v>477625</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -16793,6 +16988,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H44" s="28">
@@ -16800,23 +16996,23 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K44" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L44" s="38"/>
-      <c r="M44" s="9">
-        <v>510053</v>
-      </c>
-      <c r="N44" s="14">
-        <v>0</v>
+      <c r="M44">
+        <v>347538</v>
+      </c>
+      <c r="N44">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -16840,6 +17036,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H45" s="28">
@@ -16847,22 +17044,22 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K45" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L45" s="38"/>
-      <c r="M45" s="9">
-        <v>503866</v>
-      </c>
-      <c r="N45" s="14">
+      <c r="M45">
+        <v>530345</v>
+      </c>
+      <c r="N45">
         <v>2</v>
       </c>
     </row>
@@ -16887,6 +17084,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H46" s="28">
@@ -16894,23 +17092,23 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K46" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L46" s="38"/>
-      <c r="M46" s="9">
-        <v>524281</v>
-      </c>
-      <c r="N46" s="14">
-        <v>0</v>
+      <c r="M46">
+        <v>539088</v>
+      </c>
+      <c r="N46">
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -16934,6 +17132,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H47" s="28">
@@ -16941,23 +17140,23 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K47" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L47" s="38"/>
-      <c r="M47" s="9">
-        <v>12295833</v>
-      </c>
-      <c r="N47" s="14">
-        <v>0</v>
+      <c r="M47">
+        <v>12303072</v>
+      </c>
+      <c r="N47">
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -16981,29 +17180,30 @@
         <v>2</v>
       </c>
       <c r="G48" s="44">
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="H48" s="28">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J48">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>8</v>
       </c>
       <c r="K48" s="38">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L48" s="38"/>
-      <c r="M48" s="9">
-        <v>240048</v>
-      </c>
-      <c r="N48" s="14">
+      <c r="M48">
+        <v>408290</v>
+      </c>
+      <c r="N48">
         <v>2</v>
       </c>
     </row>
@@ -17028,30 +17228,31 @@
         <v>1</v>
       </c>
       <c r="G49" s="44">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="K49" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L49" s="38"/>
-      <c r="M49" s="9">
-        <v>246732</v>
-      </c>
-      <c r="N49" s="14">
-        <v>0</v>
+      <c r="M49">
+        <v>12295592</v>
+      </c>
+      <c r="N49">
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -17066,7 +17267,7 @@
       </c>
       <c r="D50" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="28">
         <v>0</v>
@@ -17075,30 +17276,31 @@
         <v>1</v>
       </c>
       <c r="G50" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H50" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K50" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L50" s="38"/>
-      <c r="M50" s="9">
-        <v>530334</v>
-      </c>
-      <c r="N50" s="14">
-        <v>0</v>
+      <c r="M50">
+        <v>12333237</v>
+      </c>
+      <c r="N50">
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -17122,6 +17324,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H51" s="28">
@@ -17129,23 +17332,23 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K51" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L51" s="38"/>
-      <c r="M51" s="9">
-        <v>211794</v>
-      </c>
-      <c r="N51" s="14">
-        <v>2</v>
+      <c r="M51">
+        <v>126963</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -17169,6 +17372,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H52" s="28">
@@ -17176,23 +17380,23 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K52" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L52" s="38"/>
-      <c r="M52" s="9">
-        <v>535790</v>
-      </c>
-      <c r="N52" s="14">
-        <v>3</v>
+      <c r="M52">
+        <v>543720</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -17216,6 +17420,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H53" s="28">
@@ -17223,23 +17428,23 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K53" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L53" s="38"/>
-      <c r="M53" s="9">
-        <v>62086</v>
-      </c>
-      <c r="N53" s="14">
-        <v>0</v>
+      <c r="M53">
+        <v>12295536</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -17263,6 +17468,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H54" s="28">
@@ -17270,23 +17476,23 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J54">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="K54" s="38">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L54" s="38"/>
-      <c r="M54" s="9">
-        <v>116871</v>
-      </c>
-      <c r="N54" s="14">
-        <v>5</v>
+      <c r="M54">
+        <v>12295752</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -17310,29 +17516,30 @@
         <v>18</v>
       </c>
       <c r="G55" s="44">
-        <v>79</v>
+        <f t="shared" si="2"/>
+        <v>88</v>
       </c>
       <c r="H55" s="28">
         <f t="shared" si="1"/>
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J55">
-        <f t="shared" si="3"/>
-        <v>91</v>
+        <f t="shared" si="4"/>
+        <v>88</v>
       </c>
       <c r="K55" s="38">
-        <f t="shared" si="4"/>
-        <v>-12</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L55" s="38"/>
-      <c r="M55" s="9">
-        <v>304264</v>
-      </c>
-      <c r="N55" s="14">
+      <c r="M55">
+        <v>12295724</v>
+      </c>
+      <c r="N55">
         <v>1</v>
       </c>
     </row>
@@ -17357,6 +17564,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H56" s="28">
@@ -17364,23 +17572,23 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K56" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L56" s="38"/>
-      <c r="M56" s="9">
-        <v>549259</v>
-      </c>
-      <c r="N56" s="14">
-        <v>0</v>
+      <c r="M56">
+        <v>304264</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -17404,6 +17612,7 @@
         <v>2</v>
       </c>
       <c r="G57" s="44">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="H57" s="28">
@@ -17411,23 +17620,23 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="K57" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L57" s="38"/>
-      <c r="M57" s="9">
-        <v>523938</v>
-      </c>
-      <c r="N57" s="14">
-        <v>0</v>
+      <c r="M57">
+        <v>345691</v>
+      </c>
+      <c r="N57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -17451,6 +17660,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="44">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H58" s="28">
@@ -17458,23 +17668,23 @@
         <v>2</v>
       </c>
       <c r="I58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J58">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="38">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
+      <c r="K58" s="38">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="L58" s="38"/>
-      <c r="M58" s="9">
-        <v>523849</v>
-      </c>
-      <c r="N58" s="14">
-        <v>0</v>
+      <c r="M58">
+        <v>12326118</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -17489,7 +17699,7 @@
       </c>
       <c r="D59" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="28">
         <v>0</v>
@@ -17498,30 +17708,31 @@
         <v>1</v>
       </c>
       <c r="G59" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="J59">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="K59" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L59" s="38"/>
-      <c r="M59" s="9">
-        <v>12295826</v>
-      </c>
-      <c r="N59" s="14">
-        <v>0</v>
+      <c r="M59">
+        <v>240048</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -17545,6 +17756,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H60" s="28">
@@ -17552,23 +17764,23 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K60" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L60" s="38"/>
-      <c r="M60" s="9">
-        <v>385575</v>
-      </c>
-      <c r="N60" s="14">
-        <v>0</v>
+      <c r="M60">
+        <v>199010</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -17583,7 +17795,7 @@
       </c>
       <c r="D61" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="28">
         <v>0</v>
@@ -17592,30 +17804,31 @@
         <v>1</v>
       </c>
       <c r="G61" s="44">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H61" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K61" s="38">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L61" s="38"/>
-      <c r="M61" s="9">
-        <v>12326920</v>
-      </c>
-      <c r="N61" s="14">
-        <v>0</v>
+      <c r="M61">
+        <v>12322483</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -17639,6 +17852,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="44">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H62" s="28">
@@ -17646,23 +17860,23 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J62">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K62" s="38">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
+      <c r="K62" s="38">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="L62" s="38"/>
-      <c r="M62" s="9">
-        <v>484741</v>
-      </c>
-      <c r="N62" s="14">
-        <v>0</v>
+      <c r="M62">
+        <v>401031</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -17686,6 +17900,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="44">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="H63" s="28">
@@ -17693,22 +17908,22 @@
         <v>2</v>
       </c>
       <c r="I63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J63">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="K63" s="38">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L63" s="38"/>
-      <c r="M63" s="9">
-        <v>12327316</v>
-      </c>
-      <c r="N63" s="14">
+      <c r="M63">
+        <v>529249</v>
+      </c>
+      <c r="N63">
         <v>1</v>
       </c>
     </row>
@@ -17733,6 +17948,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="44">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H64" s="28">
@@ -17740,23 +17956,23 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K64" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L64" s="38"/>
-      <c r="M64" s="9">
-        <v>12334635</v>
-      </c>
-      <c r="N64" s="14">
-        <v>0</v>
+      <c r="M64">
+        <v>12322237</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -17780,6 +17996,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H65" s="28">
@@ -17787,22 +18004,22 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K65" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L65" s="38"/>
-      <c r="M65" s="9">
-        <v>12326118</v>
-      </c>
-      <c r="N65" s="14">
+      <c r="M65">
+        <v>523194</v>
+      </c>
+      <c r="N65">
         <v>1</v>
       </c>
     </row>
@@ -17817,7 +18034,7 @@
         <v>76</v>
       </c>
       <c r="D66" s="27">
-        <f t="shared" ref="D66:D129" si="5">IF(G66&gt;0,1,0)</f>
+        <f t="shared" ref="D66:D129" si="6">IF(G66&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="E66" s="28">
@@ -17827,30 +18044,31 @@
         <v>4</v>
       </c>
       <c r="G66" s="44">
-        <v>28</v>
+        <f t="shared" si="2"/>
+        <v>26</v>
       </c>
       <c r="H66" s="28">
-        <f t="shared" ref="H66:H129" si="6">MAX(G66-F66,0)</f>
-        <v>24</v>
+        <f t="shared" ref="H66:H129" si="7">MAX(G66-F66,0)</f>
+        <v>22</v>
       </c>
       <c r="I66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J66">
-        <f t="shared" si="3"/>
-        <v>21</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="K66" s="38">
-        <f t="shared" si="4"/>
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="L66" s="38"/>
-      <c r="M66" s="9">
-        <v>345427</v>
-      </c>
-      <c r="N66" s="14">
-        <v>0</v>
+      <c r="M66">
+        <v>10466</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -17864,7 +18082,7 @@
         <v>77</v>
       </c>
       <c r="D67" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E67" s="28">
@@ -17874,30 +18092,31 @@
         <v>1</v>
       </c>
       <c r="G67" s="44">
+        <f t="shared" ref="G67:G130" si="8">J67</f>
         <v>0</v>
       </c>
       <c r="H67" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I67">
-        <f t="shared" ref="I67:I130" si="7">IF(G67&gt;=3,1,0)</f>
+        <f t="shared" ref="I67:I130" si="9">IF(G67&gt;=3,1,0)</f>
         <v>0</v>
       </c>
       <c r="J67">
-        <f t="shared" ref="J67:J130" si="8">INDEX(M:N,MATCH(B67,M:M,0),2)</f>
+        <f t="shared" ref="J67:J130" si="10">_xlfn.IFNA(INDEX(M:N,MATCH(B67,M:M,0),2),0)</f>
         <v>0</v>
       </c>
       <c r="K67" s="38">
-        <f t="shared" ref="K67:K130" si="9">G67-J67</f>
+        <f t="shared" ref="K67:K130" si="11">G67-J67</f>
         <v>0</v>
       </c>
       <c r="L67" s="38"/>
-      <c r="M67" s="9">
-        <v>499483</v>
-      </c>
-      <c r="N67" s="14">
-        <v>2</v>
+      <c r="M67">
+        <v>63887</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -17911,7 +18130,7 @@
         <v>78</v>
       </c>
       <c r="D68" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E68" s="28">
@@ -17921,30 +18140,31 @@
         <v>1</v>
       </c>
       <c r="G68" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H68" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K68" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L68" s="38"/>
-      <c r="M68" s="9">
-        <v>195918</v>
-      </c>
-      <c r="N68" s="14">
-        <v>4</v>
+      <c r="M68">
+        <v>352167</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -17958,7 +18178,7 @@
         <v>79</v>
       </c>
       <c r="D69" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E69" s="28">
@@ -17968,30 +18188,31 @@
         <v>2</v>
       </c>
       <c r="G69" s="44">
-        <v>3</v>
-      </c>
-      <c r="H69" s="28">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I69">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="J69">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
+      <c r="H69" s="28">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
       <c r="K69" s="38">
-        <f t="shared" si="9"/>
-        <v>-1</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="L69" s="38"/>
-      <c r="M69" s="9">
-        <v>126951</v>
-      </c>
-      <c r="N69" s="14">
-        <v>3</v>
+      <c r="M69">
+        <v>366702</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -18005,7 +18226,7 @@
         <v>80</v>
       </c>
       <c r="D70" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E70" s="28">
@@ -18015,29 +18236,30 @@
         <v>0</v>
       </c>
       <c r="G70" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H70" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K70" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L70" s="38"/>
-      <c r="M70" s="9">
-        <v>63887</v>
-      </c>
-      <c r="N70" s="14">
+      <c r="M70">
+        <v>486638</v>
+      </c>
+      <c r="N70">
         <v>1</v>
       </c>
     </row>
@@ -18052,7 +18274,7 @@
         <v>81</v>
       </c>
       <c r="D71" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E71" s="28">
@@ -18062,30 +18284,31 @@
         <v>2</v>
       </c>
       <c r="G71" s="44">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H71" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K71" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L71" s="38"/>
-      <c r="M71" s="9">
-        <v>229765</v>
-      </c>
-      <c r="N71" s="14">
-        <v>21</v>
+      <c r="M71">
+        <v>12312295</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -18099,7 +18322,7 @@
         <v>82</v>
       </c>
       <c r="D72" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E72" s="28">
@@ -18109,30 +18332,31 @@
         <v>1</v>
       </c>
       <c r="G72" s="44">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H72" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J72">
-        <f t="shared" si="8"/>
-        <v>2</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="K72" s="38">
-        <f t="shared" si="9"/>
-        <v>-1</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="L72" s="38"/>
-      <c r="M72" s="9">
+      <c r="M72">
         <v>574633</v>
       </c>
-      <c r="N72" s="14">
-        <v>0</v>
+      <c r="N72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -18146,7 +18370,7 @@
         <v>83</v>
       </c>
       <c r="D73" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E73" s="28">
@@ -18156,30 +18380,31 @@
         <v>1</v>
       </c>
       <c r="G73" s="44">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H73" s="28">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="H73" s="28">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
       <c r="I73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="8"/>
-        <v>2</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="K73" s="38">
-        <f t="shared" si="9"/>
-        <v>2</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="L73" s="38"/>
-      <c r="M73" s="9">
-        <v>61688</v>
-      </c>
-      <c r="N73" s="14">
-        <v>4</v>
+      <c r="M73">
+        <v>530334</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -18193,8 +18418,8 @@
         <v>84</v>
       </c>
       <c r="D74" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="E74" s="28">
         <v>0</v>
@@ -18203,30 +18428,31 @@
         <v>1</v>
       </c>
       <c r="G74" s="44">
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="H74" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="I74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J74">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>2</v>
       </c>
       <c r="K74" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L74" s="38"/>
-      <c r="M74" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="N74" s="14">
-        <v>0</v>
+      <c r="M74">
+        <v>12295717</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -18240,7 +18466,7 @@
         <v>85</v>
       </c>
       <c r="D75" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E75" s="28">
@@ -18250,29 +18476,30 @@
         <v>1</v>
       </c>
       <c r="G75" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H75" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K75" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L75" s="38"/>
-      <c r="M75" s="9">
-        <v>12295724</v>
-      </c>
-      <c r="N75" s="14">
+      <c r="M75">
+        <v>12323218</v>
+      </c>
+      <c r="N75">
         <v>1</v>
       </c>
     </row>
@@ -18287,7 +18514,7 @@
         <v>86</v>
       </c>
       <c r="D76" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E76" s="28">
@@ -18297,30 +18524,31 @@
         <v>1</v>
       </c>
       <c r="G76" s="44">
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="H76" s="28">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="I76">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="8"/>
-        <v>2</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="K76" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L76" s="38"/>
-      <c r="M76" s="9">
-        <v>12325263</v>
-      </c>
-      <c r="N76" s="14">
-        <v>0</v>
+      <c r="M76">
+        <v>368809</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -18334,7 +18562,7 @@
         <v>87</v>
       </c>
       <c r="D77" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E77" s="28">
@@ -18344,30 +18572,31 @@
         <v>1</v>
       </c>
       <c r="G77" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H77" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K77" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L77" s="38"/>
-      <c r="M77" s="9">
-        <v>12324194</v>
-      </c>
-      <c r="N77" s="14">
-        <v>0</v>
+      <c r="M77">
+        <v>562953</v>
+      </c>
+      <c r="N77">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -18381,7 +18610,7 @@
         <v>88</v>
       </c>
       <c r="D78" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E78" s="28">
@@ -18391,29 +18620,30 @@
         <v>2</v>
       </c>
       <c r="G78" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H78" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K78" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L78" s="38"/>
-      <c r="M78" s="9">
-        <v>486638</v>
-      </c>
-      <c r="N78" s="14">
+      <c r="M78">
+        <v>501263</v>
+      </c>
+      <c r="N78">
         <v>1</v>
       </c>
     </row>
@@ -18428,7 +18658,7 @@
         <v>89</v>
       </c>
       <c r="D79" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E79" s="28">
@@ -18438,29 +18668,30 @@
         <v>0</v>
       </c>
       <c r="G79" s="44">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H79" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K79" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L79" s="38"/>
-      <c r="M79" s="9">
-        <v>530058</v>
-      </c>
-      <c r="N79" s="14">
+      <c r="M79">
+        <v>222816</v>
+      </c>
+      <c r="N79">
         <v>1</v>
       </c>
     </row>
@@ -18475,8 +18706,8 @@
         <v>90</v>
       </c>
       <c r="D80" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="E80" s="28">
         <v>0</v>
@@ -18485,30 +18716,31 @@
         <v>1</v>
       </c>
       <c r="G80" s="44">
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="H80" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J80">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="K80" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L80" s="38"/>
-      <c r="M80" s="9">
-        <v>231278</v>
-      </c>
-      <c r="N80" s="14">
-        <v>0</v>
+      <c r="M80">
+        <v>519286</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -18522,8 +18754,8 @@
         <v>91</v>
       </c>
       <c r="D81" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="E81" s="28">
         <v>1</v>
@@ -18532,30 +18764,31 @@
         <v>1</v>
       </c>
       <c r="G81" s="44">
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="H81" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="I81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J81">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>2</v>
       </c>
       <c r="K81" s="38">
-        <f t="shared" si="9"/>
-        <v>-1</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="L81" s="40"/>
-      <c r="M81" s="9">
-        <v>199217</v>
-      </c>
-      <c r="N81" s="14">
-        <v>0</v>
+      <c r="M81">
+        <v>525590</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -18569,7 +18802,7 @@
         <v>92</v>
       </c>
       <c r="D82" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E82" s="28">
@@ -18579,29 +18812,30 @@
         <v>0</v>
       </c>
       <c r="G82" s="44">
-        <v>2</v>
-      </c>
-      <c r="H82" s="28">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="I82">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J82">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
+      <c r="H82" s="28">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
       <c r="K82" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L82" s="41"/>
-      <c r="M82" s="9">
-        <v>222816</v>
-      </c>
-      <c r="N82" s="14">
+      <c r="M82">
+        <v>530058</v>
+      </c>
+      <c r="N82">
         <v>1</v>
       </c>
     </row>
@@ -18616,7 +18850,7 @@
         <v>93</v>
       </c>
       <c r="D83" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E83" s="28">
@@ -18626,29 +18860,30 @@
         <v>1</v>
       </c>
       <c r="G83" s="44">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H83" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K83" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L83" s="41"/>
-      <c r="M83" s="9">
-        <v>342829</v>
-      </c>
-      <c r="N83" s="14">
+      <c r="M83">
+        <v>396176</v>
+      </c>
+      <c r="N83">
         <v>1</v>
       </c>
     </row>
@@ -18663,7 +18898,7 @@
         <v>94</v>
       </c>
       <c r="D84" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E84" s="28">
@@ -18673,30 +18908,31 @@
         <v>1</v>
       </c>
       <c r="G84" s="44">
-        <v>2</v>
-      </c>
-      <c r="H84" s="28">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I84">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J84">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
+      <c r="H84" s="28">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
       <c r="K84" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L84" s="42"/>
-      <c r="M84" s="9">
-        <v>543826</v>
-      </c>
-      <c r="N84" s="14">
-        <v>23</v>
+      <c r="M84">
+        <v>12327316</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -18710,7 +18946,7 @@
         <v>95</v>
       </c>
       <c r="D85" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E85" s="28">
@@ -18720,30 +18956,31 @@
         <v>2</v>
       </c>
       <c r="G85" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H85" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K85" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L85" s="41"/>
-      <c r="M85" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="N85" s="14">
-        <v>0</v>
+      <c r="M85">
+        <v>529090</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -18757,7 +18994,7 @@
         <v>96</v>
       </c>
       <c r="D86" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E86" s="28">
@@ -18767,29 +19004,30 @@
         <v>1</v>
       </c>
       <c r="G86" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H86" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K86" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M86" s="9">
-        <v>287622</v>
-      </c>
-      <c r="N86" s="14">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>522623</v>
+      </c>
+      <c r="N86">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -18803,7 +19041,7 @@
         <v>97</v>
       </c>
       <c r="D87" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E87" s="28">
@@ -18813,29 +19051,30 @@
         <v>0</v>
       </c>
       <c r="G87" s="44">
-        <v>4</v>
+        <f t="shared" si="8"/>
+        <v>36</v>
       </c>
       <c r="H87" s="28">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" si="7"/>
+        <v>36</v>
       </c>
       <c r="I87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="8"/>
-        <v>34</v>
+        <f t="shared" si="10"/>
+        <v>36</v>
       </c>
       <c r="K87" s="38">
-        <f t="shared" si="9"/>
-        <v>-30</v>
-      </c>
-      <c r="M87" s="9">
-        <v>542823</v>
-      </c>
-      <c r="N87" s="14">
-        <v>2</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>12301356</v>
+      </c>
+      <c r="N87">
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -18849,7 +19088,7 @@
         <v>99</v>
       </c>
       <c r="D88" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E88" s="28">
@@ -18859,29 +19098,30 @@
         <v>1</v>
       </c>
       <c r="G88" s="44">
-        <v>2</v>
-      </c>
-      <c r="H88" s="28">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I88">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J88">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
+      <c r="H88" s="28">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
       <c r="K88" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M88" s="9">
-        <v>12295887</v>
-      </c>
-      <c r="N88" s="14">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>195918</v>
+      </c>
+      <c r="N88">
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -18895,7 +19135,7 @@
         <v>101</v>
       </c>
       <c r="D89" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E89" s="28">
@@ -18905,29 +19145,30 @@
         <v>3</v>
       </c>
       <c r="G89" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H89" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K89" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M89" s="9">
-        <v>12333237</v>
-      </c>
-      <c r="N89" s="14">
-        <v>8</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>480658</v>
+      </c>
+      <c r="N89">
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -18941,7 +19182,7 @@
         <v>103</v>
       </c>
       <c r="D90" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E90" s="28">
@@ -18951,29 +19192,30 @@
         <v>1</v>
       </c>
       <c r="G90" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H90" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K90" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M90" s="9">
-        <v>477625</v>
-      </c>
-      <c r="N90" s="14">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>12332670</v>
+      </c>
+      <c r="N90">
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -18987,7 +19229,7 @@
         <v>105</v>
       </c>
       <c r="D91" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E91" s="28">
@@ -18997,30 +19239,26 @@
         <v>0</v>
       </c>
       <c r="G91" s="44">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H91" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I91">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J91">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K91" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="9">
-        <v>12295980</v>
-      </c>
-      <c r="N91" s="14">
-        <v>0</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M91" s="45"/>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="27" t="s">
@@ -19033,7 +19271,7 @@
         <v>106</v>
       </c>
       <c r="D92" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E92" s="28">
@@ -19043,30 +19281,26 @@
         <v>0</v>
       </c>
       <c r="G92" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H92" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I92">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J92">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K92" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M92" s="9">
-        <v>12295626</v>
-      </c>
-      <c r="N92" s="14">
-        <v>0</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M92" s="45"/>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="27" t="s">
@@ -19079,7 +19313,7 @@
         <v>107</v>
       </c>
       <c r="D93" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E93" s="28">
@@ -19089,30 +19323,26 @@
         <v>0</v>
       </c>
       <c r="G93" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H93" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J93">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K93" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M93" s="9">
-        <v>126963</v>
-      </c>
-      <c r="N93" s="14">
-        <v>0</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M93" s="45"/>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="27" t="s">
@@ -19125,7 +19355,7 @@
         <v>108</v>
       </c>
       <c r="D94" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E94" s="28">
@@ -19135,30 +19365,26 @@
         <v>2</v>
       </c>
       <c r="G94" s="44">
-        <v>2</v>
-      </c>
-      <c r="H94" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I94">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J94">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
+      <c r="H94" s="28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
       <c r="K94" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M94" s="9">
-        <v>199007</v>
-      </c>
-      <c r="N94" s="14">
-        <v>0</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="45"/>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="27" t="s">
@@ -19171,7 +19397,7 @@
         <v>109</v>
       </c>
       <c r="D95" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E95" s="28">
@@ -19181,30 +19407,26 @@
         <v>1</v>
       </c>
       <c r="G95" s="44">
-        <v>26</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
       <c r="H95" s="28">
-        <f t="shared" si="6"/>
-        <v>25</v>
+        <f t="shared" si="7"/>
+        <v>27</v>
       </c>
       <c r="I95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="8"/>
-        <v>20</v>
+        <f t="shared" si="10"/>
+        <v>28</v>
       </c>
       <c r="K95" s="38">
-        <f t="shared" si="9"/>
-        <v>6</v>
-      </c>
-      <c r="M95" s="9">
-        <v>12295536</v>
-      </c>
-      <c r="N95" s="14">
-        <v>1</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M95" s="45"/>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="27" t="s">
@@ -19217,7 +19439,7 @@
         <v>110</v>
       </c>
       <c r="D96" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E96" s="28">
@@ -19227,32 +19449,28 @@
         <v>0</v>
       </c>
       <c r="G96" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H96" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J96">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K96" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M96" s="9">
-        <v>213944</v>
-      </c>
-      <c r="N96" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M96" s="45"/>
+    </row>
+    <row r="97" spans="1:13">
       <c r="A97" s="27" t="s">
         <v>5</v>
       </c>
@@ -19263,7 +19481,7 @@
         <v>111</v>
       </c>
       <c r="D97" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E97" s="28">
@@ -19273,32 +19491,28 @@
         <v>1</v>
       </c>
       <c r="G97" s="44">
-        <v>3</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="H97" s="28">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="I97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="K97" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M97" s="9">
-        <v>278608</v>
-      </c>
-      <c r="N97" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M97" s="45"/>
+    </row>
+    <row r="98" spans="1:13">
       <c r="A98" s="27" t="s">
         <v>5</v>
       </c>
@@ -19309,7 +19523,7 @@
         <v>112</v>
       </c>
       <c r="D98" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E98" s="28">
@@ -19319,32 +19533,28 @@
         <v>1</v>
       </c>
       <c r="G98" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H98" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I98">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J98">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K98" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M98" s="9">
-        <v>12323463</v>
-      </c>
-      <c r="N98" s="14">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M98" s="45"/>
+    </row>
+    <row r="99" spans="1:13">
       <c r="A99" s="27" t="s">
         <v>5</v>
       </c>
@@ -19355,7 +19565,7 @@
         <v>113</v>
       </c>
       <c r="D99" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E99" s="28">
@@ -19365,308 +19575,280 @@
         <v>0</v>
       </c>
       <c r="G99" s="44">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="H99" s="28">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="K99" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M99" s="45"/>
+    </row>
+    <row r="100" spans="1:13">
+      <c r="A100" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" s="27">
+        <v>12321241</v>
+      </c>
+      <c r="C100" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="D100" s="27">
         <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="E100" s="28">
+        <v>5</v>
+      </c>
+      <c r="F100" s="36">
+        <v>3</v>
+      </c>
+      <c r="G100" s="44">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
+      <c r="H100" s="28">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="J99">
+        <v>28</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="10"/>
+        <v>31</v>
+      </c>
+      <c r="K100" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M100" s="45"/>
+    </row>
+    <row r="101" spans="1:13">
+      <c r="A101" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" s="27">
+        <v>12321243</v>
+      </c>
+      <c r="C101" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="D101" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E101" s="28">
+        <v>4</v>
+      </c>
+      <c r="F101" s="36">
+        <v>2</v>
+      </c>
+      <c r="G101" s="44">
+        <f t="shared" si="8"/>
+        <v>88</v>
+      </c>
+      <c r="H101" s="28">
+        <f t="shared" si="7"/>
+        <v>86</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <f t="shared" si="10"/>
+        <v>88</v>
+      </c>
+      <c r="K101" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M101" s="45"/>
+    </row>
+    <row r="102" spans="1:13">
+      <c r="A102" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" s="27">
+        <v>12322430</v>
+      </c>
+      <c r="C102" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D102" s="27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E102" s="28">
+        <v>0</v>
+      </c>
+      <c r="F102" s="36">
+        <v>0</v>
+      </c>
+      <c r="G102" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H102" s="28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K102" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M102" s="45"/>
+    </row>
+    <row r="103" spans="1:13">
+      <c r="A103" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" s="27">
+        <v>12324194</v>
+      </c>
+      <c r="C103" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D103" s="27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E103" s="28">
+        <v>0</v>
+      </c>
+      <c r="F103" s="36">
+        <v>0</v>
+      </c>
+      <c r="G103" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H103" s="28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K103" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M103" s="45"/>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="A104" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B104" s="27">
+        <v>12327316</v>
+      </c>
+      <c r="C104" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D104" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E104" s="28">
+        <v>0</v>
+      </c>
+      <c r="F104" s="36">
+        <v>1</v>
+      </c>
+      <c r="G104" s="44">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H104" s="28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K104" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M104" s="45"/>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B105" s="27">
+        <v>12331450</v>
+      </c>
+      <c r="C105" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D105" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E105" s="28">
+        <v>0</v>
+      </c>
+      <c r="F105" s="36">
+        <v>1</v>
+      </c>
+      <c r="G105" s="44">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="K99" s="38">
+      <c r="H105" s="28">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I105">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="M99" s="9">
-        <v>12321241</v>
-      </c>
-      <c r="N99" s="14">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14">
-      <c r="A100" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B100" s="27">
-        <v>12321241</v>
-      </c>
-      <c r="C100" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="D100" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E100" s="28">
-        <v>5</v>
-      </c>
-      <c r="F100" s="36">
-        <v>3</v>
-      </c>
-      <c r="G100" s="44">
-        <v>16</v>
-      </c>
-      <c r="H100" s="28">
-        <f t="shared" si="6"/>
-        <v>13</v>
-      </c>
-      <c r="I100">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="J100">
-        <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="K100" s="38">
-        <f t="shared" si="9"/>
-        <v>-5</v>
-      </c>
-      <c r="M100" s="9">
-        <v>287403</v>
-      </c>
-      <c r="N100" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14">
-      <c r="A101" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B101" s="27">
-        <v>12321243</v>
-      </c>
-      <c r="C101" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D101" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E101" s="28">
-        <v>4</v>
-      </c>
-      <c r="F101" s="36">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="G101" s="44">
-        <v>96</v>
-      </c>
-      <c r="H101" s="28">
-        <f t="shared" si="6"/>
-        <v>94</v>
-      </c>
-      <c r="I101">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="J101">
-        <f t="shared" si="8"/>
-        <v>90</v>
-      </c>
-      <c r="K101" s="38">
-        <f t="shared" si="9"/>
-        <v>6</v>
-      </c>
-      <c r="M101" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="N101" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14">
-      <c r="A102" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B102" s="27">
-        <v>12322430</v>
-      </c>
-      <c r="C102" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D102" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E102" s="28">
-        <v>0</v>
-      </c>
-      <c r="F102" s="36">
-        <v>0</v>
-      </c>
-      <c r="G102" s="44">
-        <v>0</v>
-      </c>
-      <c r="H102" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I102">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J102">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K102" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M102" s="9">
-        <v>511584</v>
-      </c>
-      <c r="N102" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14">
-      <c r="A103" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B103" s="27">
-        <v>12324194</v>
-      </c>
-      <c r="C103" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="D103" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E103" s="28">
-        <v>0</v>
-      </c>
-      <c r="F103" s="36">
-        <v>0</v>
-      </c>
-      <c r="G103" s="44">
-        <v>0</v>
-      </c>
-      <c r="H103" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J103">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K103" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M103" s="9">
-        <v>12295542</v>
-      </c>
-      <c r="N103" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14">
-      <c r="A104" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B104" s="27">
-        <v>12327316</v>
-      </c>
-      <c r="C104" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="D104" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E104" s="28">
-        <v>0</v>
-      </c>
-      <c r="F104" s="36">
-        <v>1</v>
-      </c>
-      <c r="G104" s="44">
-        <v>1</v>
-      </c>
-      <c r="H104" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K104" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M104" s="9">
-        <v>546446</v>
-      </c>
-      <c r="N104" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14">
-      <c r="A105" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B105" s="27">
-        <v>12331450</v>
-      </c>
-      <c r="C105" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D105" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E105" s="28">
-        <v>0</v>
-      </c>
-      <c r="F105" s="36">
-        <v>1</v>
-      </c>
-      <c r="G105" s="44">
-        <v>2</v>
-      </c>
-      <c r="H105" s="28">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I105">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J105">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
       <c r="K105" s="38">
-        <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="M105" s="9">
-        <v>199020</v>
-      </c>
-      <c r="N105" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="45"/>
+    </row>
+    <row r="106" spans="1:13">
       <c r="A106" s="27" t="s">
         <v>5</v>
       </c>
@@ -19677,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="D106" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E106" s="28">
@@ -19687,32 +19869,28 @@
         <v>1</v>
       </c>
       <c r="G106" s="44">
-        <v>2</v>
-      </c>
-      <c r="H106" s="28">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I106">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J106">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
+      <c r="H106" s="28">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
       <c r="K106" s="38">
-        <f t="shared" si="9"/>
-        <v>-3</v>
-      </c>
-      <c r="M106" s="9">
-        <v>522623</v>
-      </c>
-      <c r="N106" s="14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M106" s="45"/>
+    </row>
+    <row r="107" spans="1:13">
       <c r="A107" s="27" t="s">
         <v>5</v>
       </c>
@@ -19723,7 +19901,7 @@
         <v>121</v>
       </c>
       <c r="D107" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E107" s="28">
@@ -19733,32 +19911,28 @@
         <v>0</v>
       </c>
       <c r="G107" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H107" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I107">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J107">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K107" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M107" s="9">
-        <v>12303072</v>
-      </c>
-      <c r="N107" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M107" s="45"/>
+    </row>
+    <row r="108" spans="1:13">
       <c r="A108" s="27" t="s">
         <v>5</v>
       </c>
@@ -19769,7 +19943,7 @@
         <v>122</v>
       </c>
       <c r="D108" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E108" s="28">
@@ -19779,32 +19953,28 @@
         <v>1</v>
       </c>
       <c r="G108" s="44">
-        <v>8</v>
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="H108" s="28">
-        <f t="shared" si="6"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="I108">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J108">
-        <f t="shared" si="8"/>
-        <v>8</v>
+        <f t="shared" si="10"/>
+        <v>11</v>
       </c>
       <c r="K108" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="9">
-        <v>12295820</v>
-      </c>
-      <c r="N108" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M108" s="45"/>
+    </row>
+    <row r="109" spans="1:13">
       <c r="A109" s="27" t="s">
         <v>5</v>
       </c>
@@ -19815,8 +19985,8 @@
         <v>123</v>
       </c>
       <c r="D109" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="E109" s="28">
         <v>2</v>
@@ -19825,32 +19995,28 @@
         <v>1</v>
       </c>
       <c r="G109" s="44">
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="H109" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="I109">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J109">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>2</v>
       </c>
       <c r="K109" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M109" s="9">
-        <v>358231</v>
-      </c>
-      <c r="N109" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M109" s="45"/>
+    </row>
+    <row r="110" spans="1:13">
       <c r="A110" s="27" t="s">
         <v>5</v>
       </c>
@@ -19861,7 +20027,7 @@
         <v>124</v>
       </c>
       <c r="D110" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E110" s="28">
@@ -19871,630 +20037,574 @@
         <v>1</v>
       </c>
       <c r="G110" s="44">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="H110" s="28">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="H110" s="28">
+      <c r="I110">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="K110" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="45"/>
+    </row>
+    <row r="111" spans="1:13">
+      <c r="A111" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" s="27">
+        <v>126963</v>
+      </c>
+      <c r="C111" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D111" s="27">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="I110">
+      <c r="E111" s="28">
+        <v>0</v>
+      </c>
+      <c r="F111" s="36">
+        <v>1</v>
+      </c>
+      <c r="G111" s="44">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H111" s="28">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J110">
+      <c r="I111">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K111" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M111" s="45"/>
+    </row>
+    <row r="112" spans="1:13">
+      <c r="A112" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B112" s="27">
+        <v>127198</v>
+      </c>
+      <c r="C112" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="D112" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E112" s="28">
+        <v>0</v>
+      </c>
+      <c r="F112" s="36">
+        <v>2</v>
+      </c>
+      <c r="G112" s="44">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+      <c r="H112" s="28">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="I112">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J112">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="K112" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M112" s="45"/>
+    </row>
+    <row r="113" spans="1:13">
+      <c r="A113" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B113" s="27">
+        <v>195918</v>
+      </c>
+      <c r="C113" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D113" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E113" s="28">
+        <v>1</v>
+      </c>
+      <c r="F113" s="36">
+        <v>0</v>
+      </c>
+      <c r="G113" s="44">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H113" s="28">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="I113">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="K113" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M113" s="45"/>
+    </row>
+    <row r="114" spans="1:13">
+      <c r="A114" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B114" s="27">
+        <v>199020</v>
+      </c>
+      <c r="C114" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D114" s="27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E114" s="28">
+        <v>0</v>
+      </c>
+      <c r="F114" s="36">
+        <v>1</v>
+      </c>
+      <c r="G114" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H114" s="28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K114" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M114" s="45"/>
+    </row>
+    <row r="115" spans="1:13">
+      <c r="A115" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B115" s="27">
+        <v>240084</v>
+      </c>
+      <c r="C115" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="D115" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E115" s="28">
+        <v>0</v>
+      </c>
+      <c r="F115" s="36">
+        <v>0</v>
+      </c>
+      <c r="G115" s="44">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="H115" s="28">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="I115">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="K115" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M115" s="45"/>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B116" s="27">
+        <v>240713</v>
+      </c>
+      <c r="C116" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D116" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E116" s="28">
+        <v>1</v>
+      </c>
+      <c r="F116" s="36">
+        <v>1</v>
+      </c>
+      <c r="G116" s="44">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="H116" s="28">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="I116">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="K116" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M116" s="45"/>
+    </row>
+    <row r="117" spans="1:13">
+      <c r="A117" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" s="27">
+        <v>304264</v>
+      </c>
+      <c r="C117" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D117" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E117" s="28">
+        <v>0</v>
+      </c>
+      <c r="F117" s="36">
+        <v>1</v>
+      </c>
+      <c r="G117" s="44">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H117" s="28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K117" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M117" s="45"/>
+    </row>
+    <row r="118" spans="1:13">
+      <c r="A118" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B118" s="27">
+        <v>342829</v>
+      </c>
+      <c r="C118" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D118" s="27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E118" s="28">
+        <v>0</v>
+      </c>
+      <c r="F118" s="36">
+        <v>2</v>
+      </c>
+      <c r="G118" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H118" s="28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K118" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M118" s="45"/>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B119" s="27">
+        <v>345427</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="D119" s="27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E119" s="28">
+        <v>0</v>
+      </c>
+      <c r="F119" s="36">
+        <v>1</v>
+      </c>
+      <c r="G119" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H119" s="28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K119" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="45"/>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B120" s="27">
+        <v>352167</v>
+      </c>
+      <c r="C120" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D120" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E120" s="28">
+        <v>0</v>
+      </c>
+      <c r="F120" s="36">
+        <v>0</v>
+      </c>
+      <c r="G120" s="44">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H120" s="28">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I120">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K120" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M120" s="45"/>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B121" s="27">
+        <v>396176</v>
+      </c>
+      <c r="C121" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="D121" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E121" s="28">
+        <v>0</v>
+      </c>
+      <c r="F121" s="36">
+        <v>0</v>
+      </c>
+      <c r="G121" s="44">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H121" s="28">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I121">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K121" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M121" s="45"/>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="A122" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B122" s="27">
+        <v>401031</v>
+      </c>
+      <c r="C122" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D122" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E122" s="28">
+        <v>0</v>
+      </c>
+      <c r="F122" s="36">
+        <v>0</v>
+      </c>
+      <c r="G122" s="44">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H122" s="28">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I122">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K122" s="38">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M122" s="45"/>
+    </row>
+    <row r="123" spans="1:13">
+      <c r="A123" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B123" s="27">
+        <v>471389</v>
+      </c>
+      <c r="C123" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D123" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E123" s="28">
+        <v>0</v>
+      </c>
+      <c r="F123" s="36">
+        <v>1</v>
+      </c>
+      <c r="G123" s="44">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="K110" s="38">
+      <c r="H123" s="28">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I123">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M110" s="9">
-        <v>396176</v>
-      </c>
-      <c r="N110" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14">
-      <c r="A111" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B111" s="27">
-        <v>126963</v>
-      </c>
-      <c r="C111" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D111" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E111" s="28">
-        <v>0</v>
-      </c>
-      <c r="F111" s="36">
-        <v>1</v>
-      </c>
-      <c r="G111" s="44">
-        <v>0</v>
-      </c>
-      <c r="H111" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I111">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J111">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K111" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M111" s="9">
-        <v>539088</v>
-      </c>
-      <c r="N111" s="14">
+      <c r="J123">
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="112" spans="1:14">
-      <c r="A112" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B112" s="27">
-        <v>127198</v>
-      </c>
-      <c r="C112" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D112" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E112" s="28">
-        <v>0</v>
-      </c>
-      <c r="F112" s="36">
-        <v>2</v>
-      </c>
-      <c r="G112" s="44">
-        <v>13</v>
-      </c>
-      <c r="H112" s="28">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="I112">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="J112">
-        <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
-      <c r="K112" s="38">
-        <f t="shared" si="9"/>
-        <v>-1</v>
-      </c>
-      <c r="M112" s="9">
-        <v>525590</v>
-      </c>
-      <c r="N112" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
-      <c r="A113" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B113" s="27">
-        <v>195918</v>
-      </c>
-      <c r="C113" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="D113" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E113" s="28">
-        <v>1</v>
-      </c>
-      <c r="F113" s="36">
-        <v>0</v>
-      </c>
-      <c r="G113" s="44">
-        <v>2</v>
-      </c>
-      <c r="H113" s="28">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="I113">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="K113" s="38">
-        <f t="shared" si="9"/>
-        <v>-2</v>
-      </c>
-      <c r="M113" s="9">
-        <v>368809</v>
-      </c>
-      <c r="N113" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
-      <c r="A114" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B114" s="27">
-        <v>199020</v>
-      </c>
-      <c r="C114" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="D114" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E114" s="28">
-        <v>0</v>
-      </c>
-      <c r="F114" s="36">
-        <v>1</v>
-      </c>
-      <c r="G114" s="44">
-        <v>0</v>
-      </c>
-      <c r="H114" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I114">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K114" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M114" s="9">
-        <v>199010</v>
-      </c>
-      <c r="N114" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14">
-      <c r="A115" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B115" s="27">
-        <v>240084</v>
-      </c>
-      <c r="C115" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="D115" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E115" s="28">
-        <v>0</v>
-      </c>
-      <c r="F115" s="36">
-        <v>0</v>
-      </c>
-      <c r="G115" s="44">
-        <v>2</v>
-      </c>
-      <c r="H115" s="28">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="I115">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K115" s="38">
-        <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="M115" s="9">
-        <v>519286</v>
-      </c>
-      <c r="N115" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14">
-      <c r="A116" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B116" s="27">
-        <v>240713</v>
-      </c>
-      <c r="C116" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="D116" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E116" s="28">
-        <v>1</v>
-      </c>
-      <c r="F116" s="36">
-        <v>1</v>
-      </c>
-      <c r="G116" s="44">
-        <v>4</v>
-      </c>
-      <c r="H116" s="28">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="I116">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="J116">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K116" s="38">
-        <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="M116" s="9">
-        <v>523194</v>
-      </c>
-      <c r="N116" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14">
-      <c r="A117" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B117" s="27">
-        <v>304264</v>
-      </c>
-      <c r="C117" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="D117" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E117" s="28">
-        <v>0</v>
-      </c>
-      <c r="F117" s="36">
-        <v>1</v>
-      </c>
-      <c r="G117" s="44">
-        <v>1</v>
-      </c>
-      <c r="H117" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I117">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K117" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M117" s="9">
-        <v>61690</v>
-      </c>
-      <c r="N117" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14">
-      <c r="A118" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B118" s="27">
-        <v>342829</v>
-      </c>
-      <c r="C118" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D118" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E118" s="28">
-        <v>0</v>
-      </c>
-      <c r="F118" s="36">
-        <v>2</v>
-      </c>
-      <c r="G118" s="44">
-        <v>1</v>
-      </c>
-      <c r="H118" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K118" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M118" s="9">
-        <v>12312295</v>
-      </c>
-      <c r="N118" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14">
-      <c r="A119" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B119" s="27">
-        <v>345427</v>
-      </c>
-      <c r="C119" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="D119" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E119" s="28">
-        <v>0</v>
-      </c>
-      <c r="F119" s="36">
-        <v>1</v>
-      </c>
-      <c r="G119" s="44">
-        <v>0</v>
-      </c>
-      <c r="H119" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I119">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K119" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M119" s="9">
-        <v>12318079</v>
-      </c>
-      <c r="N119" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14">
-      <c r="A120" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B120" s="27">
-        <v>352167</v>
-      </c>
-      <c r="C120" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="D120" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E120" s="28">
-        <v>0</v>
-      </c>
-      <c r="F120" s="36">
-        <v>0</v>
-      </c>
-      <c r="G120" s="44">
-        <v>1</v>
-      </c>
-      <c r="H120" s="28">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I120">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K120" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M120" s="9">
-        <v>12321230</v>
-      </c>
-      <c r="N120" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14">
-      <c r="A121" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B121" s="27">
-        <v>396176</v>
-      </c>
-      <c r="C121" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="D121" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E121" s="28">
-        <v>0</v>
-      </c>
-      <c r="F121" s="36">
-        <v>0</v>
-      </c>
-      <c r="G121" s="44">
-        <v>1</v>
-      </c>
-      <c r="H121" s="28">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I121">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J121">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K121" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M121" s="9">
-        <v>12301356</v>
-      </c>
-      <c r="N121" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14">
-      <c r="A122" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B122" s="27">
-        <v>401031</v>
-      </c>
-      <c r="C122" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="D122" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E122" s="28">
-        <v>0</v>
-      </c>
-      <c r="F122" s="36">
-        <v>0</v>
-      </c>
-      <c r="G122" s="44">
-        <v>0</v>
-      </c>
-      <c r="H122" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K122" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M122" s="9">
-        <v>12295752</v>
-      </c>
-      <c r="N122" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14">
-      <c r="A123" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B123" s="27">
-        <v>471389</v>
-      </c>
-      <c r="C123" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D123" s="27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E123" s="28">
-        <v>0</v>
-      </c>
-      <c r="F123" s="36">
-        <v>1</v>
-      </c>
-      <c r="G123" s="44">
-        <v>1</v>
-      </c>
-      <c r="H123" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I123">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="K123" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M123" s="9">
-        <v>12313881</v>
-      </c>
-      <c r="N123" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M123" s="45"/>
+    </row>
+    <row r="124" spans="1:13">
       <c r="A124" s="27" t="s">
         <v>5</v>
       </c>
@@ -20505,7 +20615,7 @@
         <v>138</v>
       </c>
       <c r="D124" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E124" s="28">
@@ -20515,32 +20625,28 @@
         <v>0</v>
       </c>
       <c r="G124" s="44">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="H124" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="I124">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J124">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>2</v>
       </c>
       <c r="K124" s="38">
-        <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="M124" s="9">
-        <v>12302808</v>
-      </c>
-      <c r="N124" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M124" s="45"/>
+    </row>
+    <row r="125" spans="1:13">
       <c r="A125" s="27" t="s">
         <v>5</v>
       </c>
@@ -20551,7 +20657,7 @@
         <v>139</v>
       </c>
       <c r="D125" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E125" s="28">
@@ -20561,32 +20667,28 @@
         <v>1</v>
       </c>
       <c r="G125" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H125" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I125">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J125">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K125" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M125" s="9">
-        <v>12334637</v>
-      </c>
-      <c r="N125" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M125" s="45"/>
+    </row>
+    <row r="126" spans="1:13">
       <c r="A126" s="27" t="s">
         <v>5</v>
       </c>
@@ -20597,7 +20699,7 @@
         <v>140</v>
       </c>
       <c r="D126" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E126" s="28">
@@ -20607,32 +20709,28 @@
         <v>0</v>
       </c>
       <c r="G126" s="44">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="H126" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="I126">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J126">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>2</v>
       </c>
       <c r="K126" s="38">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="M126" s="9">
-        <v>471389</v>
-      </c>
-      <c r="N126" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M126" s="45"/>
+    </row>
+    <row r="127" spans="1:13">
       <c r="A127" s="27" t="s">
         <v>5</v>
       </c>
@@ -20643,7 +20741,7 @@
         <v>141</v>
       </c>
       <c r="D127" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E127" s="28">
@@ -20653,32 +20751,28 @@
         <v>1</v>
       </c>
       <c r="G127" s="44">
-        <v>2</v>
-      </c>
-      <c r="H127" s="28">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I127">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J127">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
+      <c r="H127" s="28">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I127">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
       <c r="K127" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M127" s="9">
-        <v>529249</v>
-      </c>
-      <c r="N127" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M127" s="45"/>
+    </row>
+    <row r="128" spans="1:13">
       <c r="A128" s="27" t="s">
         <v>5</v>
       </c>
@@ -20689,7 +20783,7 @@
         <v>142</v>
       </c>
       <c r="D128" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E128" s="28">
@@ -20699,32 +20793,28 @@
         <v>1</v>
       </c>
       <c r="G128" s="44">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H128" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J128">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K128" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M128" s="9">
-        <v>366702</v>
-      </c>
-      <c r="N128" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="45"/>
+    </row>
+    <row r="129" spans="1:13">
       <c r="A129" s="27" t="s">
         <v>5</v>
       </c>
@@ -20735,7 +20825,7 @@
         <v>143</v>
       </c>
       <c r="D129" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E129" s="28">
@@ -20745,32 +20835,28 @@
         <v>1</v>
       </c>
       <c r="G129" s="44">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H129" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I129">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J129">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K129" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M129" s="9">
-        <v>514589</v>
-      </c>
-      <c r="N129" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M129" s="45"/>
+    </row>
+    <row r="130" spans="1:13">
       <c r="A130" s="27" t="s">
         <v>5</v>
       </c>
@@ -20781,7 +20867,7 @@
         <v>144</v>
       </c>
       <c r="D130" s="27">
-        <f t="shared" ref="D130:D146" si="10">IF(G130&gt;0,1,0)</f>
+        <f t="shared" ref="D130:D146" si="12">IF(G130&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="E130" s="28">
@@ -20791,32 +20877,28 @@
         <v>1</v>
       </c>
       <c r="G130" s="44">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="H130" s="28">
+        <f t="shared" ref="H130:H146" si="13">MAX(G130-F130,0)</f>
         <v>2</v>
       </c>
-      <c r="H130" s="28">
-        <f t="shared" ref="H130:H146" si="11">MAX(G130-F130,0)</f>
-        <v>1</v>
-      </c>
       <c r="I130">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="J130">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="K130" s="38">
-        <f t="shared" si="9"/>
-        <v>-1</v>
-      </c>
-      <c r="M130" s="9">
-        <v>401031</v>
-      </c>
-      <c r="N130" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M130" s="45"/>
+    </row>
+    <row r="131" spans="1:13">
       <c r="A131" s="27" t="s">
         <v>5</v>
       </c>
@@ -20827,7 +20909,7 @@
         <v>145</v>
       </c>
       <c r="D131" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E131" s="28">
@@ -20837,32 +20919,28 @@
         <v>1</v>
       </c>
       <c r="G131" s="44">
+        <f t="shared" ref="G131:G146" si="14">J131</f>
         <v>0</v>
       </c>
       <c r="H131" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I131">
-        <f t="shared" ref="I131:I146" si="12">IF(G131&gt;=3,1,0)</f>
+        <f t="shared" ref="I131:I146" si="15">IF(G131&gt;=3,1,0)</f>
         <v>0</v>
       </c>
       <c r="J131">
-        <f t="shared" ref="J131:J146" si="13">INDEX(M:N,MATCH(B131,M:M,0),2)</f>
+        <f t="shared" ref="J131:J146" si="16">_xlfn.IFNA(INDEX(M:N,MATCH(B131,M:M,0),2),0)</f>
         <v>0</v>
       </c>
       <c r="K131" s="38">
-        <f t="shared" ref="K131:K146" si="14">G131-J131</f>
-        <v>0</v>
-      </c>
-      <c r="M131" s="9">
-        <v>562953</v>
-      </c>
-      <c r="N131" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14">
+        <f t="shared" ref="K131:K146" si="17">G131-J131</f>
+        <v>0</v>
+      </c>
+      <c r="M131" s="45"/>
+    </row>
+    <row r="132" spans="1:13">
       <c r="A132" s="27" t="s">
         <v>5</v>
       </c>
@@ -20873,7 +20951,7 @@
         <v>146</v>
       </c>
       <c r="D132" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E132" s="28">
@@ -20883,32 +20961,28 @@
         <v>0</v>
       </c>
       <c r="G132" s="44">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H132" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I132">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J132">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K132" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M132" s="9">
-        <v>529090</v>
-      </c>
-      <c r="N132" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M132" s="45"/>
+    </row>
+    <row r="133" spans="1:13">
       <c r="A133" s="27" t="s">
         <v>5</v>
       </c>
@@ -20919,7 +20993,7 @@
         <v>147</v>
       </c>
       <c r="D133" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E133" s="28">
@@ -20929,32 +21003,28 @@
         <v>1</v>
       </c>
       <c r="G133" s="44">
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="H133" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="I133">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J133">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="K133" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M133" s="9">
-        <v>345691</v>
-      </c>
-      <c r="N133" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M133" s="45"/>
+    </row>
+    <row r="134" spans="1:13">
       <c r="A134" s="27" t="s">
         <v>5</v>
       </c>
@@ -20965,8 +21035,8 @@
         <v>148</v>
       </c>
       <c r="D134" s="27">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="E134" s="28">
         <v>0</v>
@@ -20975,32 +21045,28 @@
         <v>1</v>
       </c>
       <c r="G134" s="44">
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>2</v>
       </c>
       <c r="H134" s="28">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="I134">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J134">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>2</v>
       </c>
       <c r="K134" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M134" s="9">
-        <v>347538</v>
-      </c>
-      <c r="N134" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M134" s="45"/>
+    </row>
+    <row r="135" spans="1:13">
       <c r="A135" s="27" t="s">
         <v>5</v>
       </c>
@@ -21011,7 +21077,7 @@
         <v>149</v>
       </c>
       <c r="D135" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E135" s="28">
@@ -21021,32 +21087,28 @@
         <v>1</v>
       </c>
       <c r="G135" s="44">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H135" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I135">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J135">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K135" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M135" s="9">
-        <v>301600</v>
-      </c>
-      <c r="N135" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M135" s="45"/>
+    </row>
+    <row r="136" spans="1:13">
       <c r="A136" s="27" t="s">
         <v>5</v>
       </c>
@@ -21057,7 +21119,7 @@
         <v>150</v>
       </c>
       <c r="D136" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E136" s="28">
@@ -21067,32 +21129,28 @@
         <v>2</v>
       </c>
       <c r="G136" s="44">
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="H136" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="I136">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J136">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="K136" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M136" s="9">
-        <v>563095</v>
-      </c>
-      <c r="N136" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M136" s="45"/>
+    </row>
+    <row r="137" spans="1:13">
       <c r="A137" s="27" t="s">
         <v>5</v>
       </c>
@@ -21103,7 +21161,7 @@
         <v>151</v>
       </c>
       <c r="D137" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E137" s="28">
@@ -21113,32 +21171,28 @@
         <v>1</v>
       </c>
       <c r="G137" s="44">
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H137" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I137">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J137">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="K137" s="38">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="M137" s="9">
-        <v>480658</v>
-      </c>
-      <c r="N137" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M137" s="45"/>
+    </row>
+    <row r="138" spans="1:13">
       <c r="A138" s="27" t="s">
         <v>5</v>
       </c>
@@ -21149,7 +21203,7 @@
         <v>152</v>
       </c>
       <c r="D138" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E138" s="28">
@@ -21159,32 +21213,28 @@
         <v>1</v>
       </c>
       <c r="G138" s="44">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H138" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I138">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J138">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K138" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M138" s="9">
-        <v>543720</v>
-      </c>
-      <c r="N138" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M138" s="45"/>
+    </row>
+    <row r="139" spans="1:13">
       <c r="A139" s="27" t="s">
         <v>5</v>
       </c>
@@ -21195,7 +21245,7 @@
         <v>153</v>
       </c>
       <c r="D139" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E139" s="28">
@@ -21205,32 +21255,28 @@
         <v>0</v>
       </c>
       <c r="G139" s="44">
-        <v>21</v>
+        <f t="shared" si="14"/>
+        <v>28</v>
       </c>
       <c r="H139" s="28">
-        <f t="shared" si="11"/>
-        <v>21</v>
+        <f t="shared" si="13"/>
+        <v>28</v>
       </c>
       <c r="I139">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J139">
-        <f t="shared" si="13"/>
-        <v>23</v>
+        <f t="shared" si="16"/>
+        <v>28</v>
       </c>
       <c r="K139" s="38">
-        <f t="shared" si="14"/>
-        <v>-2</v>
-      </c>
-      <c r="M139" s="9">
-        <v>352167</v>
-      </c>
-      <c r="N139" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M139" s="45"/>
+    </row>
+    <row r="140" spans="1:13">
       <c r="A140" s="27" t="s">
         <v>5</v>
       </c>
@@ -21241,7 +21287,7 @@
         <v>154</v>
       </c>
       <c r="D140" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E140" s="28">
@@ -21251,32 +21297,28 @@
         <v>0</v>
       </c>
       <c r="G140" s="44">
-        <v>2</v>
+        <f t="shared" si="14"/>
+        <v>3</v>
       </c>
       <c r="H140" s="28">
-        <f t="shared" si="11"/>
-        <v>2</v>
+        <f t="shared" si="13"/>
+        <v>3</v>
       </c>
       <c r="I140">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="J140">
-        <f t="shared" si="13"/>
-        <v>2</v>
+        <f t="shared" si="16"/>
+        <v>3</v>
       </c>
       <c r="K140" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M140" s="9">
-        <v>526916</v>
-      </c>
-      <c r="N140" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M140" s="45"/>
+    </row>
+    <row r="141" spans="1:13">
       <c r="A141" s="27" t="s">
         <v>5</v>
       </c>
@@ -21287,7 +21329,7 @@
         <v>155</v>
       </c>
       <c r="D141" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E141" s="28">
@@ -21297,32 +21339,28 @@
         <v>0</v>
       </c>
       <c r="G141" s="44">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H141" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I141">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J141">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K141" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M141" s="9">
-        <v>491288</v>
-      </c>
-      <c r="N141" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M141" s="45"/>
+    </row>
+    <row r="142" spans="1:13">
       <c r="A142" s="27" t="s">
         <v>5</v>
       </c>
@@ -21333,7 +21371,7 @@
         <v>156</v>
       </c>
       <c r="D142" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E142" s="28">
@@ -21343,32 +21381,28 @@
         <v>0</v>
       </c>
       <c r="G142" s="44">
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H142" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="I142">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J142">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="K142" s="38">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="M142" s="9">
-        <v>501141</v>
-      </c>
-      <c r="N142" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M142" s="45"/>
+    </row>
+    <row r="143" spans="1:13">
       <c r="A143" s="27" t="s">
         <v>5</v>
       </c>
@@ -21379,7 +21413,7 @@
         <v>157</v>
       </c>
       <c r="D143" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E143" s="28">
@@ -21389,32 +21423,28 @@
         <v>1</v>
       </c>
       <c r="G143" s="44">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H143" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I143">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J143">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K143" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M143" s="9">
-        <v>240084</v>
-      </c>
-      <c r="N143" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M143" s="45"/>
+    </row>
+    <row r="144" spans="1:13">
       <c r="A144" s="27" t="s">
         <v>5</v>
       </c>
@@ -21425,7 +21455,7 @@
         <v>158</v>
       </c>
       <c r="D144" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E144" s="28">
@@ -21435,32 +21465,28 @@
         <v>0</v>
       </c>
       <c r="G144" s="44">
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H144" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="I144">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J144">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="K144" s="38">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="M144" s="9">
-        <v>12324647</v>
-      </c>
-      <c r="N144" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M144" s="45"/>
+    </row>
+    <row r="145" spans="1:13">
       <c r="A145" s="27" t="s">
         <v>5</v>
       </c>
@@ -21471,7 +21497,7 @@
         <v>159</v>
       </c>
       <c r="D145" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E145" s="28">
@@ -21481,32 +21507,28 @@
         <v>1</v>
       </c>
       <c r="G145" s="44">
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="H145" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="I145">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J145">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="K145" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M145" s="9">
-        <v>503633</v>
-      </c>
-      <c r="N145" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M145" s="45"/>
+    </row>
+    <row r="146" spans="1:13">
       <c r="A146" s="27" t="s">
         <v>5</v>
       </c>
@@ -21517,7 +21539,7 @@
         <v>97</v>
       </c>
       <c r="D146" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E146" s="28">
@@ -21527,30 +21549,161 @@
         <v>0</v>
       </c>
       <c r="G146" s="44">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H146" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I146">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J146">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K146" s="38">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M146" s="9">
-        <v>12322430</v>
-      </c>
-      <c r="N146" s="14">
-        <v>0</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M146" s="45"/>
+    </row>
+    <row r="147" spans="1:13">
+      <c r="M147" s="45"/>
+    </row>
+    <row r="148" spans="1:13">
+      <c r="M148" s="45"/>
+    </row>
+    <row r="149" spans="1:13">
+      <c r="M149" s="45"/>
+    </row>
+    <row r="150" spans="1:13">
+      <c r="M150" s="45"/>
+    </row>
+    <row r="151" spans="1:13">
+      <c r="M151" s="45"/>
+    </row>
+    <row r="152" spans="1:13">
+      <c r="M152" s="45"/>
+    </row>
+    <row r="153" spans="1:13">
+      <c r="M153" s="45"/>
+    </row>
+    <row r="154" spans="1:13">
+      <c r="M154" s="45"/>
+    </row>
+    <row r="155" spans="1:13">
+      <c r="M155" s="45"/>
+    </row>
+    <row r="156" spans="1:13">
+      <c r="M156" s="45"/>
+    </row>
+    <row r="157" spans="1:13">
+      <c r="M157" s="45"/>
+    </row>
+    <row r="158" spans="1:13">
+      <c r="M158" s="45"/>
+    </row>
+    <row r="159" spans="1:13">
+      <c r="M159" s="45"/>
+    </row>
+    <row r="160" spans="1:13">
+      <c r="M160" s="45"/>
+    </row>
+    <row r="161" spans="13:13">
+      <c r="M161" s="45"/>
+    </row>
+    <row r="162" spans="13:13">
+      <c r="M162" s="45"/>
+    </row>
+    <row r="163" spans="13:13">
+      <c r="M163" s="45"/>
+    </row>
+    <row r="164" spans="13:13">
+      <c r="M164" s="45"/>
+    </row>
+    <row r="165" spans="13:13">
+      <c r="M165" s="45"/>
+    </row>
+    <row r="166" spans="13:13">
+      <c r="M166" s="45"/>
+    </row>
+    <row r="167" spans="13:13">
+      <c r="M167" s="45"/>
+    </row>
+    <row r="168" spans="13:13">
+      <c r="M168" s="45"/>
+    </row>
+    <row r="169" spans="13:13">
+      <c r="M169" s="45"/>
+    </row>
+    <row r="170" spans="13:13">
+      <c r="M170" s="45"/>
+    </row>
+    <row r="171" spans="13:13">
+      <c r="M171" s="45"/>
+    </row>
+    <row r="172" spans="13:13">
+      <c r="M172" s="45"/>
+    </row>
+    <row r="173" spans="13:13">
+      <c r="M173" s="45"/>
+    </row>
+    <row r="174" spans="13:13">
+      <c r="M174" s="45"/>
+    </row>
+    <row r="175" spans="13:13">
+      <c r="M175" s="45"/>
+    </row>
+    <row r="176" spans="13:13">
+      <c r="M176" s="45"/>
+    </row>
+    <row r="177" spans="13:13">
+      <c r="M177" s="45"/>
+    </row>
+    <row r="178" spans="13:13">
+      <c r="M178" s="45"/>
+    </row>
+    <row r="179" spans="13:13">
+      <c r="M179" s="45"/>
+    </row>
+    <row r="180" spans="13:13">
+      <c r="M180" s="45"/>
+    </row>
+    <row r="181" spans="13:13">
+      <c r="M181" s="45"/>
+    </row>
+    <row r="182" spans="13:13">
+      <c r="M182" s="45"/>
+    </row>
+    <row r="183" spans="13:13">
+      <c r="M183" s="45"/>
+    </row>
+    <row r="184" spans="13:13">
+      <c r="M184" s="45"/>
+    </row>
+    <row r="185" spans="13:13">
+      <c r="M185" s="45"/>
+    </row>
+    <row r="186" spans="13:13">
+      <c r="M186" s="45"/>
+    </row>
+    <row r="187" spans="13:13">
+      <c r="M187" s="45"/>
+    </row>
+    <row r="188" spans="13:13">
+      <c r="M188" s="45"/>
+    </row>
+    <row r="189" spans="13:13">
+      <c r="M189" s="45"/>
+    </row>
+    <row r="190" spans="13:13">
+      <c r="M190" s="45"/>
+    </row>
+    <row r="191" spans="13:13">
+      <c r="M191" s="45"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K146" xr:uid="{F42E2FEA-7579-4105-BB5C-707DD11104C2}"/>
